--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$126</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$115</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4857" uniqueCount="700">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4433" uniqueCount="689">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-14T12:31:04+00:00</t>
+    <t>2025-03-04T08:19:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1633,9 +1633,6 @@
   </si>
   <si>
     <t>Observation.dataAbsentReason.coding.code</t>
-  </si>
-  <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
   </si>
   <si>
     <t>Observation.dataAbsentReason.coding.display</t>
@@ -1980,40 +1977,10 @@
     <t>Need to be able to identify the target population for proper interpretation.</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J148-ReferenceRangeAppliesTo-CISIS/FHIR/JDV-J148-ReferenceRangeAppliesTo-CISIS</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.appliesTo.id</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.appliesTo.extension</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.appliesTo.coding</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.appliesTo.coding.id</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.appliesTo.coding.extension</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.appliesTo.coding.system</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.appliesTo.coding.version</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.appliesTo.coding.code</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.appliesTo.coding.display</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.appliesTo.coding.userSelected</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.appliesTo.text</t>
+    <t>Codes identifying the population the reference range applies to.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -2513,11 +2480,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP126"/>
+  <dimension ref="A1:AP115"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="56.09375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="56.09375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="51.109375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="49.3046875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="26.921875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
@@ -2540,8 +2507,8 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="112.42578125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="112.42578125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="98.61328125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="93.578125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -5057,7 +5024,7 @@
         <v>81</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>205</v>
+        <v>82</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>122</v>
@@ -11089,7 +11056,7 @@
         <v>81</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>205</v>
+        <v>82</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>122</v>
@@ -11104,7 +11071,7 @@
         <v>82</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>196</v>
+        <v>111</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
@@ -11211,7 +11178,7 @@
         <v>81</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>205</v>
+        <v>82</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>105</v>
@@ -11449,7 +11416,7 @@
         <v>81</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>205</v>
+        <v>82</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>122</v>
@@ -11464,7 +11431,7 @@
         <v>82</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>196</v>
+        <v>111</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
@@ -11571,7 +11538,7 @@
         <v>93</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>205</v>
+        <v>82</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>105</v>
@@ -11691,7 +11658,7 @@
         <v>93</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>205</v>
+        <v>82</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>105</v>
@@ -11751,9 +11718,7 @@
       <c r="M77" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="N77" t="s" s="2">
-        <v>521</v>
-      </c>
+      <c r="N77" s="2"/>
       <c r="O77" t="s" s="2">
         <v>315</v>
       </c>
@@ -11813,7 +11778,7 @@
         <v>93</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>205</v>
+        <v>82</v>
       </c>
       <c r="AJ77" t="s" s="2">
         <v>105</v>
@@ -11839,10 +11804,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11873,9 +11838,7 @@
       <c r="M78" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="N78" t="s" s="2">
-        <v>521</v>
-      </c>
+      <c r="N78" s="2"/>
       <c r="O78" t="s" s="2">
         <v>324</v>
       </c>
@@ -11935,7 +11898,7 @@
         <v>93</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>205</v>
+        <v>82</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>105</v>
@@ -11961,10 +11924,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12057,7 +12020,7 @@
         <v>93</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>205</v>
+        <v>82</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>105</v>
@@ -12083,10 +12046,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12179,7 +12142,7 @@
         <v>93</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>205</v>
+        <v>82</v>
       </c>
       <c r="AJ80" t="s" s="2">
         <v>105</v>
@@ -12205,14 +12168,14 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -12234,16 +12197,16 @@
         <v>264</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="M81" t="s" s="2">
         <v>527</v>
       </c>
-      <c r="M81" t="s" s="2">
+      <c r="N81" t="s" s="2">
         <v>528</v>
       </c>
-      <c r="N81" t="s" s="2">
+      <c r="O81" t="s" s="2">
         <v>529</v>
-      </c>
-      <c r="O81" t="s" s="2">
-        <v>530</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>82</v>
@@ -12272,7 +12235,7 @@
       </c>
       <c r="Y81" s="2"/>
       <c r="Z81" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>82</v>
@@ -12290,7 +12253,7 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -12308,27 +12271,27 @@
         <v>82</v>
       </c>
       <c r="AL81" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="AM81" t="s" s="2">
         <v>532</v>
       </c>
-      <c r="AM81" t="s" s="2">
+      <c r="AN81" t="s" s="2">
         <v>533</v>
       </c>
-      <c r="AN81" t="s" s="2">
+      <c r="AO81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP81" t="s" s="2">
         <v>534</v>
-      </c>
-      <c r="AO81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP81" t="s" s="2">
-        <v>535</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12351,19 +12314,19 @@
         <v>82</v>
       </c>
       <c r="K82" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="L82" t="s" s="2">
         <v>537</v>
       </c>
-      <c r="L82" t="s" s="2">
+      <c r="M82" t="s" s="2">
         <v>538</v>
       </c>
-      <c r="M82" t="s" s="2">
+      <c r="N82" t="s" s="2">
         <v>539</v>
       </c>
-      <c r="N82" t="s" s="2">
+      <c r="O82" t="s" s="2">
         <v>540</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>541</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>82</v>
@@ -12412,7 +12375,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12433,10 +12396,10 @@
         <v>82</v>
       </c>
       <c r="AM82" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="AN82" t="s" s="2">
         <v>542</v>
-      </c>
-      <c r="AN82" t="s" s="2">
-        <v>543</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>82</v>
@@ -12447,10 +12410,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12476,13 +12439,13 @@
         <v>264</v>
       </c>
       <c r="L83" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>545</v>
       </c>
-      <c r="M83" t="s" s="2">
+      <c r="N83" t="s" s="2">
         <v>546</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>547</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -12512,7 +12475,7 @@
       </c>
       <c r="Y83" s="2"/>
       <c r="Z83" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>82</v>
@@ -12530,7 +12493,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12548,27 +12511,27 @@
         <v>82</v>
       </c>
       <c r="AL83" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="AM83" t="s" s="2">
         <v>549</v>
       </c>
-      <c r="AM83" t="s" s="2">
+      <c r="AN83" t="s" s="2">
         <v>550</v>
       </c>
-      <c r="AN83" t="s" s="2">
+      <c r="AO83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP83" t="s" s="2">
         <v>551</v>
-      </c>
-      <c r="AO83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP83" t="s" s="2">
-        <v>552</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12683,10 +12646,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12803,10 +12766,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12870,7 +12833,7 @@
       </c>
       <c r="Y86" s="2"/>
       <c r="Z86" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>82</v>
@@ -12923,10 +12886,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13045,10 +13008,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13074,16 +13037,16 @@
         <v>264</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="M88" t="s" s="2">
         <v>559</v>
       </c>
-      <c r="M88" t="s" s="2">
+      <c r="N88" t="s" s="2">
         <v>560</v>
       </c>
-      <c r="N88" t="s" s="2">
+      <c r="O88" t="s" s="2">
         <v>561</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>562</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>82</v>
@@ -13112,7 +13075,7 @@
       </c>
       <c r="Y88" s="2"/>
       <c r="Z88" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>82</v>
@@ -13130,7 +13093,7 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -13151,10 +13114,10 @@
         <v>82</v>
       </c>
       <c r="AM88" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="AN88" t="s" s="2">
         <v>564</v>
-      </c>
-      <c r="AN88" t="s" s="2">
-        <v>565</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>82</v>
@@ -13165,10 +13128,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13283,10 +13246,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13403,10 +13366,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13470,7 +13433,7 @@
       </c>
       <c r="Y91" s="2"/>
       <c r="Z91" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>82</v>
@@ -13523,10 +13486,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13645,10 +13608,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13671,16 +13634,16 @@
         <v>82</v>
       </c>
       <c r="K93" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="L93" t="s" s="2">
         <v>572</v>
       </c>
-      <c r="L93" t="s" s="2">
+      <c r="M93" t="s" s="2">
         <v>573</v>
       </c>
-      <c r="M93" t="s" s="2">
+      <c r="N93" t="s" s="2">
         <v>574</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>575</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13730,7 +13693,7 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13748,27 +13711,27 @@
         <v>82</v>
       </c>
       <c r="AL93" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="AM93" t="s" s="2">
         <v>576</v>
       </c>
-      <c r="AM93" t="s" s="2">
+      <c r="AN93" t="s" s="2">
         <v>577</v>
       </c>
-      <c r="AN93" t="s" s="2">
+      <c r="AO93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP93" t="s" s="2">
         <v>578</v>
-      </c>
-      <c r="AO93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP93" t="s" s="2">
-        <v>579</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13791,16 +13754,16 @@
         <v>82</v>
       </c>
       <c r="K94" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="L94" t="s" s="2">
         <v>581</v>
       </c>
-      <c r="L94" t="s" s="2">
+      <c r="M94" t="s" s="2">
         <v>582</v>
       </c>
-      <c r="M94" t="s" s="2">
+      <c r="N94" t="s" s="2">
         <v>583</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>584</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13850,7 +13813,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13868,27 +13831,27 @@
         <v>82</v>
       </c>
       <c r="AL94" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="AM94" t="s" s="2">
         <v>585</v>
       </c>
-      <c r="AM94" t="s" s="2">
+      <c r="AN94" t="s" s="2">
         <v>586</v>
       </c>
-      <c r="AN94" t="s" s="2">
+      <c r="AO94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP94" t="s" s="2">
         <v>587</v>
-      </c>
-      <c r="AO94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP94" t="s" s="2">
-        <v>588</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13911,19 +13874,19 @@
         <v>82</v>
       </c>
       <c r="K95" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="L95" t="s" s="2">
         <v>590</v>
       </c>
-      <c r="L95" t="s" s="2">
+      <c r="M95" t="s" s="2">
         <v>591</v>
       </c>
-      <c r="M95" t="s" s="2">
+      <c r="N95" t="s" s="2">
         <v>592</v>
       </c>
-      <c r="N95" t="s" s="2">
+      <c r="O95" t="s" s="2">
         <v>593</v>
-      </c>
-      <c r="O95" t="s" s="2">
-        <v>594</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>82</v>
@@ -13972,7 +13935,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -13984,19 +13947,19 @@
         <v>82</v>
       </c>
       <c r="AJ95" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="AK95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM95" t="s" s="2">
         <v>595</v>
       </c>
-      <c r="AK95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM95" t="s" s="2">
+      <c r="AN95" t="s" s="2">
         <v>596</v>
-      </c>
-      <c r="AN95" t="s" s="2">
-        <v>597</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>82</v>
@@ -14007,10 +13970,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14125,10 +14088,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14245,14 +14208,14 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
@@ -14274,10 +14237,10 @@
         <v>114</v>
       </c>
       <c r="L98" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="M98" t="s" s="2">
         <v>602</v>
-      </c>
-      <c r="M98" t="s" s="2">
-        <v>603</v>
       </c>
       <c r="N98" t="s" s="2">
         <v>117</v>
@@ -14332,7 +14295,7 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -14367,10 +14330,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14393,13 +14356,13 @@
         <v>82</v>
       </c>
       <c r="K99" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="L99" t="s" s="2">
         <v>606</v>
       </c>
-      <c r="L99" t="s" s="2">
+      <c r="M99" t="s" s="2">
         <v>607</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>608</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -14450,7 +14413,7 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -14459,7 +14422,7 @@
         <v>93</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="AJ99" t="s" s="2">
         <v>105</v>
@@ -14471,10 +14434,10 @@
         <v>82</v>
       </c>
       <c r="AM99" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="AN99" t="s" s="2">
         <v>610</v>
-      </c>
-      <c r="AN99" t="s" s="2">
-        <v>611</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>82</v>
@@ -14485,10 +14448,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14511,13 +14474,13 @@
         <v>82</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="L100" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="M100" t="s" s="2">
         <v>613</v>
-      </c>
-      <c r="M100" t="s" s="2">
-        <v>614</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -14568,7 +14531,7 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14577,7 +14540,7 @@
         <v>93</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="AJ100" t="s" s="2">
         <v>105</v>
@@ -14589,10 +14552,10 @@
         <v>82</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>82</v>
@@ -14603,10 +14566,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14632,16 +14595,16 @@
         <v>264</v>
       </c>
       <c r="L101" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="M101" t="s" s="2">
         <v>617</v>
       </c>
-      <c r="M101" t="s" s="2">
+      <c r="N101" t="s" s="2">
         <v>618</v>
       </c>
-      <c r="N101" t="s" s="2">
+      <c r="O101" t="s" s="2">
         <v>619</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>620</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>82</v>
@@ -14669,11 +14632,11 @@
         <v>177</v>
       </c>
       <c r="Y101" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="Z101" t="s" s="2">
         <v>621</v>
       </c>
-      <c r="Z101" t="s" s="2">
-        <v>622</v>
-      </c>
       <c r="AA101" t="s" s="2">
         <v>82</v>
       </c>
@@ -14690,7 +14653,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14708,13 +14671,13 @@
         <v>82</v>
       </c>
       <c r="AL101" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="AM101" t="s" s="2">
         <v>623</v>
       </c>
-      <c r="AM101" t="s" s="2">
-        <v>624</v>
-      </c>
       <c r="AN101" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>82</v>
@@ -14725,10 +14688,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14754,16 +14717,16 @@
         <v>264</v>
       </c>
       <c r="L102" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="M102" t="s" s="2">
         <v>626</v>
       </c>
-      <c r="M102" t="s" s="2">
+      <c r="N102" t="s" s="2">
         <v>627</v>
       </c>
-      <c r="N102" t="s" s="2">
+      <c r="O102" t="s" s="2">
         <v>628</v>
-      </c>
-      <c r="O102" t="s" s="2">
-        <v>629</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>82</v>
@@ -14788,10 +14751,10 @@
         <v>82</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>256</v>
+        <v>163</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="Z102" t="s" s="2">
         <v>630</v>
@@ -14812,7 +14775,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14830,13 +14793,13 @@
         <v>82</v>
       </c>
       <c r="AL102" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="AM102" t="s" s="2">
         <v>623</v>
       </c>
-      <c r="AM102" t="s" s="2">
-        <v>624</v>
-      </c>
       <c r="AN102" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>82</v>
@@ -14873,16 +14836,18 @@
         <v>82</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>107</v>
+        <v>632</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>108</v>
+        <v>633</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>109</v>
+        <v>634</v>
       </c>
       <c r="N103" s="2"/>
-      <c r="O103" s="2"/>
+      <c r="O103" t="s" s="2">
+        <v>635</v>
+      </c>
       <c r="P103" t="s" s="2">
         <v>82</v>
       </c>
@@ -14930,7 +14895,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>110</v>
+        <v>631</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -14942,7 +14907,7 @@
         <v>82</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>82</v>
@@ -14954,7 +14919,7 @@
         <v>82</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>111</v>
+        <v>636</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>82</v>
@@ -14965,21 +14930,21 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>632</v>
+        <v>637</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>632</v>
+        <v>637</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H104" t="s" s="2">
         <v>82</v>
@@ -14991,17 +14956,15 @@
         <v>82</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>115</v>
+        <v>638</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>639</v>
+      </c>
+      <c r="N104" s="2"/>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
         <v>82</v>
@@ -15038,31 +15001,31 @@
         <v>82</v>
       </c>
       <c r="AB104" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC104" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD104" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE104" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>121</v>
+        <v>637</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>205</v>
+        <v>82</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>82</v>
@@ -15071,10 +15034,10 @@
         <v>82</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>82</v>
+        <v>609</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>196</v>
+        <v>640</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>82</v>
@@ -15085,10 +15048,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>633</v>
+        <v>641</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>633</v>
+        <v>641</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15111,20 +15074,18 @@
         <v>94</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>151</v>
+        <v>642</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>282</v>
+        <v>643</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>283</v>
+        <v>644</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="O105" t="s" s="2">
-        <v>285</v>
-      </c>
+        <v>645</v>
+      </c>
+      <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
         <v>82</v>
       </c>
@@ -15172,7 +15133,7 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>286</v>
+        <v>641</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -15181,7 +15142,7 @@
         <v>81</v>
       </c>
       <c r="AI105" t="s" s="2">
-        <v>205</v>
+        <v>82</v>
       </c>
       <c r="AJ105" t="s" s="2">
         <v>105</v>
@@ -15193,10 +15154,10 @@
         <v>82</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>287</v>
+        <v>646</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>288</v>
+        <v>647</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>82</v>
@@ -15207,10 +15168,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>634</v>
+        <v>648</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>634</v>
+        <v>648</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15221,7 +15182,7 @@
         <v>80</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>82</v>
@@ -15230,18 +15191,20 @@
         <v>82</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>107</v>
+        <v>649</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>108</v>
+        <v>650</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N106" s="2"/>
+        <v>651</v>
+      </c>
+      <c r="N106" t="s" s="2">
+        <v>652</v>
+      </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
         <v>82</v>
@@ -15290,19 +15253,19 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>110</v>
+        <v>648</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>82</v>
@@ -15311,10 +15274,10 @@
         <v>82</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>82</v>
+        <v>646</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>111</v>
+        <v>653</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>82</v>
@@ -15325,14 +15288,14 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>635</v>
+        <v>654</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>635</v>
+        <v>654</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
@@ -15342,27 +15305,29 @@
         <v>81</v>
       </c>
       <c r="H107" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I107" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>114</v>
+        <v>589</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>115</v>
+        <v>655</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>116</v>
+        <v>655</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O107" s="2"/>
+        <v>656</v>
+      </c>
+      <c r="O107" t="s" s="2">
+        <v>657</v>
+      </c>
       <c r="P107" t="s" s="2">
         <v>82</v>
       </c>
@@ -15398,19 +15363,19 @@
         <v>82</v>
       </c>
       <c r="AB107" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC107" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD107" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE107" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>121</v>
+        <v>654</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15419,10 +15384,10 @@
         <v>81</v>
       </c>
       <c r="AI107" t="s" s="2">
-        <v>205</v>
+        <v>82</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>122</v>
+        <v>658</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>82</v>
@@ -15431,10 +15396,10 @@
         <v>82</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>82</v>
+        <v>659</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>196</v>
+        <v>660</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>82</v>
@@ -15445,10 +15410,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>636</v>
+        <v>661</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>636</v>
+        <v>661</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15456,7 +15421,7 @@
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G108" t="s" s="2">
         <v>93</v>
@@ -15468,23 +15433,19 @@
         <v>82</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>295</v>
+        <v>108</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N108" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="O108" t="s" s="2">
-        <v>298</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N108" s="2"/>
+      <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
         <v>82</v>
       </c>
@@ -15532,7 +15493,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>300</v>
+        <v>110</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15541,10 +15502,10 @@
         <v>93</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>205</v>
+        <v>82</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK108" t="s" s="2">
         <v>82</v>
@@ -15553,10 +15514,10 @@
         <v>82</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>301</v>
+        <v>82</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>302</v>
+        <v>111</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>82</v>
@@ -15567,21 +15528,21 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>637</v>
+        <v>662</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>637</v>
+        <v>662</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H109" t="s" s="2">
         <v>82</v>
@@ -15590,19 +15551,19 @@
         <v>82</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>305</v>
+        <v>115</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>306</v>
+        <v>116</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>307</v>
+        <v>117</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -15652,19 +15613,19 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>308</v>
+        <v>121</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI109" t="s" s="2">
-        <v>205</v>
+        <v>82</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK109" t="s" s="2">
         <v>82</v>
@@ -15673,10 +15634,10 @@
         <v>82</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>309</v>
+        <v>82</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>310</v>
+        <v>111</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>82</v>
@@ -15687,45 +15648,45 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>638</v>
+        <v>663</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>638</v>
+        <v>663</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>82</v>
+        <v>600</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H110" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I110" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J110" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>173</v>
+        <v>114</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>313</v>
+        <v>601</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>314</v>
+        <v>602</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>521</v>
+        <v>117</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>315</v>
+        <v>222</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>82</v>
@@ -15774,19 +15735,19 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>317</v>
+        <v>603</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI110" t="s" s="2">
-        <v>205</v>
+        <v>82</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK110" t="s" s="2">
         <v>82</v>
@@ -15795,10 +15756,10 @@
         <v>82</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>318</v>
+        <v>82</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>319</v>
+        <v>196</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>82</v>
@@ -15809,10 +15770,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>639</v>
+        <v>664</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>639</v>
+        <v>664</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15820,13 +15781,13 @@
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G111" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H111" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I111" t="s" s="2">
         <v>82</v>
@@ -15835,19 +15796,19 @@
         <v>94</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>107</v>
+        <v>264</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>322</v>
+        <v>665</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>323</v>
+        <v>666</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>521</v>
+        <v>667</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>324</v>
+        <v>668</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>82</v>
@@ -15872,13 +15833,13 @@
         <v>82</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>82</v>
+        <v>353</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>82</v>
+        <v>354</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>82</v>
@@ -15896,16 +15857,16 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>325</v>
+        <v>664</v>
       </c>
       <c r="AG111" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH111" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AI111" t="s" s="2">
-        <v>205</v>
+        <v>82</v>
       </c>
       <c r="AJ111" t="s" s="2">
         <v>105</v>
@@ -15914,16 +15875,16 @@
         <v>82</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>82</v>
+        <v>669</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>326</v>
+        <v>357</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>327</v>
+        <v>358</v>
       </c>
       <c r="AO111" t="s" s="2">
-        <v>82</v>
+        <v>359</v>
       </c>
       <c r="AP111" t="s" s="2">
         <v>82</v>
@@ -15931,10 +15892,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>640</v>
+        <v>670</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>640</v>
+        <v>670</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15948,7 +15909,7 @@
         <v>93</v>
       </c>
       <c r="H112" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I112" t="s" s="2">
         <v>82</v>
@@ -15957,19 +15918,19 @@
         <v>94</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>330</v>
+        <v>671</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>331</v>
+        <v>672</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>332</v>
+        <v>673</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>333</v>
+        <v>674</v>
       </c>
       <c r="O112" t="s" s="2">
-        <v>334</v>
+        <v>444</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>82</v>
@@ -15994,13 +15955,13 @@
         <v>82</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>82</v>
+        <v>675</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>82</v>
+        <v>676</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>82</v>
@@ -16018,7 +15979,7 @@
         <v>82</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>335</v>
+        <v>670</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -16027,7 +15988,7 @@
         <v>93</v>
       </c>
       <c r="AI112" t="s" s="2">
-        <v>205</v>
+        <v>677</v>
       </c>
       <c r="AJ112" t="s" s="2">
         <v>105</v>
@@ -16036,27 +15997,27 @@
         <v>82</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>82</v>
+        <v>678</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>336</v>
+        <v>449</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>337</v>
+        <v>450</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP112" t="s" s="2">
-        <v>82</v>
+        <v>451</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>641</v>
+        <v>679</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>641</v>
+        <v>679</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16070,28 +16031,28 @@
         <v>93</v>
       </c>
       <c r="H113" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I113" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>107</v>
+        <v>264</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>340</v>
+        <v>680</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>341</v>
+        <v>681</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>342</v>
+        <v>682</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>343</v>
+        <v>508</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>82</v>
@@ -16116,13 +16077,13 @@
         <v>82</v>
       </c>
       <c r="X113" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="Y113" t="s" s="2">
-        <v>82</v>
+        <v>509</v>
       </c>
       <c r="Z113" t="s" s="2">
-        <v>82</v>
+        <v>510</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>82</v>
@@ -16140,7 +16101,7 @@
         <v>82</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>344</v>
+        <v>679</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -16149,7 +16110,7 @@
         <v>93</v>
       </c>
       <c r="AI113" t="s" s="2">
-        <v>205</v>
+        <v>683</v>
       </c>
       <c r="AJ113" t="s" s="2">
         <v>105</v>
@@ -16161,10 +16122,10 @@
         <v>82</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>345</v>
+        <v>196</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>346</v>
+        <v>512</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>82</v>
@@ -16175,21 +16136,21 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>642</v>
+        <v>684</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>642</v>
+        <v>684</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
-        <v>82</v>
+        <v>525</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>82</v>
@@ -16201,17 +16162,19 @@
         <v>82</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>643</v>
+        <v>264</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>644</v>
+        <v>526</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>645</v>
-      </c>
-      <c r="N114" s="2"/>
+        <v>527</v>
+      </c>
+      <c r="N114" t="s" s="2">
+        <v>528</v>
+      </c>
       <c r="O114" t="s" s="2">
-        <v>646</v>
+        <v>529</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>82</v>
@@ -16236,13 +16199,13 @@
         <v>82</v>
       </c>
       <c r="X114" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="Y114" t="s" s="2">
-        <v>82</v>
+        <v>685</v>
       </c>
       <c r="Z114" t="s" s="2">
-        <v>82</v>
+        <v>530</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>82</v>
@@ -16260,13 +16223,13 @@
         <v>82</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>642</v>
+        <v>684</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI114" t="s" s="2">
         <v>82</v>
@@ -16278,27 +16241,27 @@
         <v>82</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>82</v>
+        <v>531</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>82</v>
+        <v>532</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>647</v>
+        <v>533</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP114" t="s" s="2">
-        <v>82</v>
+        <v>534</v>
       </c>
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>648</v>
+        <v>686</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>648</v>
+        <v>686</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16309,7 +16272,7 @@
         <v>80</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H115" t="s" s="2">
         <v>82</v>
@@ -16321,16 +16284,20 @@
         <v>82</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>649</v>
+        <v>687</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="N115" s="2"/>
-      <c r="O115" s="2"/>
+        <v>688</v>
+      </c>
+      <c r="N115" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="O115" t="s" s="2">
+        <v>593</v>
+      </c>
       <c r="P115" t="s" s="2">
         <v>82</v>
       </c>
@@ -16378,13 +16345,13 @@
         <v>82</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>648</v>
+        <v>686</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH115" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI115" t="s" s="2">
         <v>82</v>
@@ -16399,1352 +16366,20 @@
         <v>82</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>610</v>
+        <v>595</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>651</v>
+        <v>596</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP115" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="116" hidden="true">
-      <c r="A116" t="s" s="2">
-        <v>652</v>
-      </c>
-      <c r="B116" t="s" s="2">
-        <v>652</v>
-      </c>
-      <c r="C116" s="2"/>
-      <c r="D116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E116" s="2"/>
-      <c r="F116" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G116" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J116" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K116" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="L116" t="s" s="2">
-        <v>654</v>
-      </c>
-      <c r="M116" t="s" s="2">
-        <v>655</v>
-      </c>
-      <c r="N116" t="s" s="2">
-        <v>656</v>
-      </c>
-      <c r="O116" s="2"/>
-      <c r="P116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q116" s="2"/>
-      <c r="R116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF116" t="s" s="2">
-        <v>652</v>
-      </c>
-      <c r="AG116" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH116" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ116" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM116" t="s" s="2">
-        <v>657</v>
-      </c>
-      <c r="AN116" t="s" s="2">
-        <v>658</v>
-      </c>
-      <c r="AO116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP116" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="117" hidden="true">
-      <c r="A117" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="B117" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="C117" s="2"/>
-      <c r="D117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E117" s="2"/>
-      <c r="F117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G117" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J117" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K117" t="s" s="2">
-        <v>660</v>
-      </c>
-      <c r="L117" t="s" s="2">
-        <v>661</v>
-      </c>
-      <c r="M117" t="s" s="2">
-        <v>662</v>
-      </c>
-      <c r="N117" t="s" s="2">
-        <v>663</v>
-      </c>
-      <c r="O117" s="2"/>
-      <c r="P117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q117" s="2"/>
-      <c r="R117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF117" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="AG117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH117" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ117" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM117" t="s" s="2">
-        <v>657</v>
-      </c>
-      <c r="AN117" t="s" s="2">
-        <v>664</v>
-      </c>
-      <c r="AO117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP117" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="118" hidden="true">
-      <c r="A118" t="s" s="2">
-        <v>665</v>
-      </c>
-      <c r="B118" t="s" s="2">
-        <v>665</v>
-      </c>
-      <c r="C118" s="2"/>
-      <c r="D118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E118" s="2"/>
-      <c r="F118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G118" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H118" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="I118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J118" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K118" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="L118" t="s" s="2">
-        <v>666</v>
-      </c>
-      <c r="M118" t="s" s="2">
-        <v>666</v>
-      </c>
-      <c r="N118" t="s" s="2">
-        <v>667</v>
-      </c>
-      <c r="O118" t="s" s="2">
-        <v>668</v>
-      </c>
-      <c r="P118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q118" s="2"/>
-      <c r="R118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF118" t="s" s="2">
-        <v>665</v>
-      </c>
-      <c r="AG118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH118" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ118" t="s" s="2">
-        <v>669</v>
-      </c>
-      <c r="AK118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM118" t="s" s="2">
-        <v>670</v>
-      </c>
-      <c r="AN118" t="s" s="2">
-        <v>671</v>
-      </c>
-      <c r="AO118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP118" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="119" hidden="true">
-      <c r="A119" t="s" s="2">
-        <v>672</v>
-      </c>
-      <c r="B119" t="s" s="2">
-        <v>672</v>
-      </c>
-      <c r="C119" s="2"/>
-      <c r="D119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E119" s="2"/>
-      <c r="F119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G119" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K119" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="L119" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="M119" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N119" s="2"/>
-      <c r="O119" s="2"/>
-      <c r="P119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q119" s="2"/>
-      <c r="R119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF119" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="AG119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH119" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN119" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="AO119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP119" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="120" hidden="true">
-      <c r="A120" t="s" s="2">
-        <v>673</v>
-      </c>
-      <c r="B120" t="s" s="2">
-        <v>673</v>
-      </c>
-      <c r="C120" s="2"/>
-      <c r="D120" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="E120" s="2"/>
-      <c r="F120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G120" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K120" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="L120" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="M120" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N120" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O120" s="2"/>
-      <c r="P120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q120" s="2"/>
-      <c r="R120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF120" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="AG120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH120" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ120" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="AK120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN120" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="AO120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP120" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="121" hidden="true">
-      <c r="A121" t="s" s="2">
-        <v>674</v>
-      </c>
-      <c r="B121" t="s" s="2">
-        <v>674</v>
-      </c>
-      <c r="C121" s="2"/>
-      <c r="D121" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="E121" s="2"/>
-      <c r="F121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G121" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I121" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="J121" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K121" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="L121" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="M121" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="N121" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O121" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="P121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q121" s="2"/>
-      <c r="R121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF121" t="s" s="2">
-        <v>604</v>
-      </c>
-      <c r="AG121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH121" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ121" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="AK121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN121" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="AO121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP121" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="122" hidden="true">
-      <c r="A122" t="s" s="2">
-        <v>675</v>
-      </c>
-      <c r="B122" t="s" s="2">
-        <v>675</v>
-      </c>
-      <c r="C122" s="2"/>
-      <c r="D122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E122" s="2"/>
-      <c r="F122" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="G122" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H122" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="I122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J122" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K122" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="L122" t="s" s="2">
-        <v>676</v>
-      </c>
-      <c r="M122" t="s" s="2">
-        <v>677</v>
-      </c>
-      <c r="N122" t="s" s="2">
-        <v>678</v>
-      </c>
-      <c r="O122" t="s" s="2">
-        <v>679</v>
-      </c>
-      <c r="P122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q122" s="2"/>
-      <c r="R122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X122" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="Y122" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="Z122" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="AA122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF122" t="s" s="2">
-        <v>675</v>
-      </c>
-      <c r="AG122" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AH122" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ122" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL122" t="s" s="2">
-        <v>680</v>
-      </c>
-      <c r="AM122" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="AN122" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="AO122" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="AP122" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="123" hidden="true">
-      <c r="A123" t="s" s="2">
-        <v>681</v>
-      </c>
-      <c r="B123" t="s" s="2">
-        <v>681</v>
-      </c>
-      <c r="C123" s="2"/>
-      <c r="D123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E123" s="2"/>
-      <c r="F123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G123" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H123" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="I123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J123" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K123" t="s" s="2">
-        <v>682</v>
-      </c>
-      <c r="L123" t="s" s="2">
-        <v>683</v>
-      </c>
-      <c r="M123" t="s" s="2">
-        <v>684</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>685</v>
-      </c>
-      <c r="O123" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="P123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q123" s="2"/>
-      <c r="R123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X123" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="Y123" t="s" s="2">
-        <v>686</v>
-      </c>
-      <c r="Z123" t="s" s="2">
-        <v>687</v>
-      </c>
-      <c r="AA123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF123" t="s" s="2">
-        <v>681</v>
-      </c>
-      <c r="AG123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH123" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI123" t="s" s="2">
-        <v>688</v>
-      </c>
-      <c r="AJ123" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL123" t="s" s="2">
-        <v>689</v>
-      </c>
-      <c r="AM123" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="AN123" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="AO123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP123" t="s" s="2">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="124" hidden="true">
-      <c r="A124" t="s" s="2">
-        <v>690</v>
-      </c>
-      <c r="B124" t="s" s="2">
-        <v>690</v>
-      </c>
-      <c r="C124" s="2"/>
-      <c r="D124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E124" s="2"/>
-      <c r="F124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G124" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H124" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="I124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K124" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="L124" t="s" s="2">
-        <v>691</v>
-      </c>
-      <c r="M124" t="s" s="2">
-        <v>692</v>
-      </c>
-      <c r="N124" t="s" s="2">
-        <v>693</v>
-      </c>
-      <c r="O124" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="P124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q124" s="2"/>
-      <c r="R124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X124" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="Y124" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="Z124" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="AA124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF124" t="s" s="2">
-        <v>690</v>
-      </c>
-      <c r="AG124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH124" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI124" t="s" s="2">
-        <v>694</v>
-      </c>
-      <c r="AJ124" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM124" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="AN124" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="AO124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP124" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="125" hidden="true">
-      <c r="A125" t="s" s="2">
-        <v>695</v>
-      </c>
-      <c r="B125" t="s" s="2">
-        <v>695</v>
-      </c>
-      <c r="C125" s="2"/>
-      <c r="D125" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="E125" s="2"/>
-      <c r="F125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G125" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K125" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="L125" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="M125" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="N125" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="O125" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="P125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q125" s="2"/>
-      <c r="R125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X125" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="Y125" t="s" s="2">
-        <v>696</v>
-      </c>
-      <c r="Z125" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="AA125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF125" t="s" s="2">
-        <v>695</v>
-      </c>
-      <c r="AG125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH125" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ125" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL125" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="AM125" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="AN125" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="AO125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP125" t="s" s="2">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="126" hidden="true">
-      <c r="A126" t="s" s="2">
-        <v>697</v>
-      </c>
-      <c r="B126" t="s" s="2">
-        <v>697</v>
-      </c>
-      <c r="C126" s="2"/>
-      <c r="D126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E126" s="2"/>
-      <c r="F126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G126" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K126" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="L126" t="s" s="2">
-        <v>698</v>
-      </c>
-      <c r="M126" t="s" s="2">
-        <v>699</v>
-      </c>
-      <c r="N126" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="O126" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="P126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q126" s="2"/>
-      <c r="R126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF126" t="s" s="2">
-        <v>697</v>
-      </c>
-      <c r="AG126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH126" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ126" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM126" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="AN126" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="AO126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP126" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP126">
+  <autoFilter ref="A1:AP115">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -17754,7 +16389,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI125">
+  <conditionalFormatting sqref="A2:AI114">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-04T08:19:08+00:00</t>
+    <t>2025-03-27T13:15:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-27T13:15:18+00:00</t>
+    <t>2025-03-27T14:27:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-27T14:27:05+00:00</t>
+    <t>2025-03-27T15:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-27T15:41:15+00:00</t>
+    <t>2025-03-27T15:45:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-27T15:45:03+00:00</t>
+    <t>2025-03-27T15:47:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-27T15:47:29+00:00</t>
+    <t>2025-03-31T07:44:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T07:44:46+00:00</t>
+    <t>2025-03-31T07:48:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T07:48:14+00:00</t>
+    <t>2025-03-31T07:48:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T07:48:39+00:00</t>
+    <t>2025-03-31T11:47:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T11:47:14+00:00</t>
+    <t>2025-03-31T11:46:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T11:46:38+00:00</t>
+    <t>2025-03-31T14:05:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T14:05:37+00:00</t>
+    <t>2025-03-31T15:50:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T15:50:51+00:00</t>
+    <t>2025-03-31T15:55:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T15:55:12+00:00</t>
+    <t>2025-03-31T16:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T16:04:27+00:00</t>
+    <t>2025-03-31T16:16:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T16:16:40+00:00</t>
+    <t>2025-03-31T16:26:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T16:26:20+00:00</t>
+    <t>2025-03-31T16:37:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T16:37:23+00:00</t>
+    <t>2025-04-01T07:11:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-01T07:11:22+00:00</t>
+    <t>2025-04-01T07:12:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-01T07:12:21+00:00</t>
+    <t>2025-04-01T07:12:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-02T12:26:08+00:00</t>
+    <t>2025-07-07T09:50:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-07T09:50:30+00:00</t>
+    <t>2025-12-23T16:18:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -4928,7 +4928,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
         <v>210</v>
       </c>
@@ -5650,7 +5650,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
         <v>251</v>
       </c>
@@ -5890,7 +5890,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
         <v>274</v>
       </c>
@@ -6252,7 +6252,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
         <v>280</v>
       </c>
@@ -6612,7 +6612,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
         <v>293</v>
       </c>
@@ -6854,7 +6854,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
         <v>311</v>
       </c>
@@ -7338,7 +7338,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
         <v>347</v>
       </c>
@@ -8906,7 +8906,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="54" hidden="true">
+    <row r="54">
       <c r="A54" t="s" s="2">
         <v>384</v>
       </c>
@@ -9270,7 +9270,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="57" hidden="true">
+    <row r="57">
       <c r="A57" t="s" s="2">
         <v>411</v>
       </c>
@@ -9752,7 +9752,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="61" hidden="true">
+    <row r="61">
       <c r="A61" t="s" s="2">
         <v>452</v>
       </c>
@@ -10114,7 +10114,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
         <v>458</v>
       </c>
@@ -10358,7 +10358,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="66" hidden="true">
+    <row r="66">
       <c r="A66" t="s" s="2">
         <v>479</v>
       </c>
@@ -10478,7 +10478,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="67" hidden="true">
+    <row r="67">
       <c r="A67" t="s" s="2">
         <v>487</v>
       </c>
@@ -10598,7 +10598,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="68" hidden="true">
+    <row r="68">
       <c r="A68" t="s" s="2">
         <v>496</v>
       </c>
@@ -10720,7 +10720,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="69" hidden="true">
+    <row r="69">
       <c r="A69" t="s" s="2">
         <v>504</v>
       </c>
@@ -13006,7 +13006,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="88" hidden="true">
+    <row r="88">
       <c r="A88" t="s" s="2">
         <v>557</v>
       </c>
@@ -13726,7 +13726,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="94" hidden="true">
+    <row r="94">
       <c r="A94" t="s" s="2">
         <v>579</v>
       </c>
@@ -15286,7 +15286,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="107" hidden="true">
+    <row r="107">
       <c r="A107" t="s" s="2">
         <v>654</v>
       </c>
@@ -15768,7 +15768,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="111" hidden="true">
+    <row r="111">
       <c r="A111" t="s" s="2">
         <v>664</v>
       </c>
@@ -15890,7 +15890,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="112" hidden="true">
+    <row r="112">
       <c r="A112" t="s" s="2">
         <v>670</v>
       </c>
@@ -16012,7 +16012,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="113" hidden="true">
+    <row r="113">
       <c r="A113" t="s" s="2">
         <v>679</v>
       </c>
@@ -16380,12 +16380,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AP115">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-23T16:18:55+00:00</t>
+    <t>2026-01-06T09:57:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-06T09:57:05+00:00</t>
+    <t>2026-01-06T10:01:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$115</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$117</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4433" uniqueCount="689">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4509" uniqueCount="699">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-06T10:01:17+00:00</t>
+    <t>2026-01-19T08:51:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -439,7 +439,7 @@
 </t>
   </si>
   <si>
-    <t>Uri identifiant les systèmes tiers ayant envoyé la ressource. L’uri est sous la forme d’un oid : « urn:oid:xx.xx.xx »</t>
+    <t>Uri identifiant les systèmes tiers ayant envoyé la ressource. L’uri est sous la forme d’une oid : « urn:oid:xx.xx.xx »</t>
   </si>
   <si>
     <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
@@ -686,7 +686,40 @@
     <t>Other information that may be relevant to this event.</t>
   </si>
   <si>
-    <t>Other resources *from the patient record* that may be relevant to the event.  The information from these resources was either used to create the instance or is provided to help with its interpretation.  This extension **should not** be used if more specific  inline elements  or extensions are available.  For example, use `Observation.hasMember`  instead of supportingInformation for  representing the members of an Observation panel.</t>
+    <t>Autres ressources pertinentes *du dossier patient*</t>
+  </si>
+  <si>
+    <t>Observation.extension:MesReasonForMeasurement</t>
+  </si>
+  <si>
+    <t>MesReasonForMeasurement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-reason-for-measurement}
+</t>
+  </si>
+  <si>
+    <t>Motif de la mesure</t>
+  </si>
+  <si>
+    <t>Motif de la mesure
+Texte libre (ex. diabète, surpoids, hypercholestérolémie, risque cardiovasculaire, suivi, ...)</t>
+  </si>
+  <si>
+    <t>Observation.extension:MesOriginOfData</t>
+  </si>
+  <si>
+    <t>MesOriginOfData</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-origin-of-data}
+</t>
+  </si>
+  <si>
+    <t>Origine de la donnée</t>
+  </si>
+  <si>
+    <t>Extension pour tracer l'origine de la donnée issue d'un compte rendu de biologie (CR-Bio).</t>
   </si>
   <si>
     <t>Observation.extension:MesMomentOfMeasurement</t>
@@ -1360,7 +1393,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CareTeam|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|PractitionerRole|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-related-person)
+    <t xml:space="preserve">Reference(CareTeam|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-related-person|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|PractitionerRole|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
 </t>
   </si>
   <si>
@@ -2480,12 +2513,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP115"/>
+  <dimension ref="A1:AP117"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="43.81640625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="42.26953125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="23.08203125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="23.171875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -5084,7 +5117,7 @@
         <v>218</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -5170,46 +5203,44 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="C23" s="2"/>
+        <v>197</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>221</v>
+      </c>
       <c r="D23" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>114</v>
+        <v>222</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>222</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>82</v>
       </c>
@@ -5257,7 +5288,7 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>223</v>
+        <v>200</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -5281,7 +5312,7 @@
         <v>82</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>196</v>
+        <v>82</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>82</v>
@@ -5292,12 +5323,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="C24" s="2"/>
+        <v>197</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>226</v>
+      </c>
       <c r="D24" t="s" s="2">
         <v>82</v>
       </c>
@@ -5306,7 +5339,7 @@
         <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>82</v>
@@ -5315,21 +5348,19 @@
         <v>82</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="N24" s="2"/>
-      <c r="O24" t="s" s="2">
-        <v>228</v>
-      </c>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>82</v>
       </c>
@@ -5377,7 +5408,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>224</v>
+        <v>200</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -5389,22 +5420,22 @@
         <v>82</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>229</v>
+        <v>82</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>230</v>
+        <v>82</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>231</v>
+        <v>82</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>232</v>
+        <v>82</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>82</v>
@@ -5412,14 +5443,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>234</v>
+        <v>113</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -5432,23 +5463,25 @@
         <v>82</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>235</v>
+        <v>114</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="N25" s="2"/>
+        <v>231</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O25" t="s" s="2">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
@@ -5509,19 +5542,19 @@
         <v>82</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>239</v>
+        <v>82</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>240</v>
+        <v>82</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>241</v>
+        <v>196</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>82</v>
@@ -5532,14 +5565,14 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>243</v>
+        <v>82</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -5558,18 +5591,18 @@
         <v>94</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="O26" s="2"/>
+        <v>237</v>
+      </c>
+      <c r="N26" s="2"/>
+      <c r="O26" t="s" s="2">
+        <v>238</v>
+      </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
       </c>
@@ -5617,7 +5650,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5632,65 +5665,63 @@
         <v>105</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>82</v>
+        <v>242</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>82</v>
+        <v>244</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J27" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>173</v>
+        <v>245</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>254</v>
-      </c>
+        <v>247</v>
+      </c>
+      <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>82</v>
@@ -5715,11 +5746,13 @@
         <v>82</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="Y27" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z27" t="s" s="2">
-        <v>257</v>
+        <v>82</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>82</v>
@@ -5737,13 +5770,13 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>82</v>
@@ -5752,19 +5785,19 @@
         <v>105</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>259</v>
+        <v>82</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>262</v>
+        <v>82</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>82</v>
@@ -5772,46 +5805,44 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>82</v>
+        <v>253</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J28" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="I28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J28" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K28" t="s" s="2">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>268</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>82</v>
       </c>
@@ -5835,29 +5866,31 @@
         <v>82</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>269</v>
+        <v>82</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>270</v>
+        <v>82</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="AC28" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5872,19 +5905,19 @@
         <v>105</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>82</v>
+        <v>258</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>82</v>
+        <v>259</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>273</v>
+        <v>82</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>82</v>
@@ -5892,14 +5925,12 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>274</v>
+        <v>261</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="C29" t="s" s="2">
-        <v>275</v>
-      </c>
+        <v>261</v>
+      </c>
+      <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
         <v>82</v>
       </c>
@@ -5914,25 +5945,25 @@
         <v>94</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="N29" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>82</v>
@@ -5957,13 +5988,11 @@
         <v>82</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="Y29" t="s" s="2">
-        <v>269</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="Y29" s="2"/>
       <c r="Z29" t="s" s="2">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>82</v>
@@ -5981,13 +6010,13 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>82</v>
@@ -5996,19 +6025,19 @@
         <v>105</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>82</v>
+        <v>268</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>82</v>
+        <v>269</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>82</v>
+        <v>270</v>
       </c>
       <c r="AN29" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AO29" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="AO29" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>82</v>
@@ -6016,10 +6045,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6027,13 +6056,13 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>82</v>
@@ -6042,16 +6071,20 @@
         <v>82</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>107</v>
+        <v>274</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>108</v>
+        <v>275</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
+        <v>276</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>278</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>82</v>
       </c>
@@ -6075,43 +6108,41 @@
         <v>82</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>82</v>
+        <v>279</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>82</v>
+        <v>280</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>281</v>
+      </c>
+      <c r="AC30" s="2"/>
       <c r="AD30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>110</v>
+        <v>273</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>82</v>
@@ -6123,35 +6154,37 @@
         <v>82</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>111</v>
+        <v>282</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>82</v>
+        <v>283</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="C31" s="2"/>
+        <v>273</v>
+      </c>
+      <c r="C31" t="s" s="2">
+        <v>285</v>
+      </c>
       <c r="D31" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>82</v>
@@ -6160,18 +6193,20 @@
         <v>82</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>114</v>
+        <v>274</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>115</v>
+        <v>275</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>116</v>
+        <v>276</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O31" s="2"/>
+        <v>277</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>278</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>82</v>
       </c>
@@ -6195,31 +6230,31 @@
         <v>82</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>82</v>
+        <v>279</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>82</v>
+        <v>280</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>121</v>
+        <v>273</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -6231,7 +6266,7 @@
         <v>82</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>82</v>
@@ -6243,21 +6278,21 @@
         <v>82</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>111</v>
+        <v>282</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>82</v>
+        <v>283</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6265,35 +6300,31 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G32" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="G32" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="H32" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>151</v>
+        <v>107</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>282</v>
+        <v>108</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>285</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>82</v>
       </c>
@@ -6341,19 +6372,19 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>286</v>
+        <v>110</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>82</v>
@@ -6362,10 +6393,10 @@
         <v>82</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>287</v>
+        <v>82</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>288</v>
+        <v>111</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>82</v>
@@ -6376,21 +6407,21 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="B33" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="B33" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>82</v>
@@ -6402,15 +6433,17 @@
         <v>82</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N33" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -6447,31 +6480,31 @@
         <v>82</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>82</v>
@@ -6492,46 +6525,48 @@
         <v>82</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="B34" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="B34" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>114</v>
+        <v>151</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>115</v>
+        <v>292</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>116</v>
+        <v>293</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O34" s="2"/>
+        <v>294</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>295</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
       </c>
@@ -6567,19 +6602,19 @@
         <v>82</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>121</v>
+        <v>296</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6591,7 +6626,7 @@
         <v>82</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>82</v>
@@ -6600,10 +6635,10 @@
         <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>82</v>
+        <v>297</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>111</v>
+        <v>298</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
@@ -6612,12 +6647,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6625,41 +6660,37 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>295</v>
+        <v>108</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>298</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>299</v>
+        <v>82</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>82</v>
@@ -6701,7 +6732,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>300</v>
+        <v>110</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6713,7 +6744,7 @@
         <v>82</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>82</v>
@@ -6722,10 +6753,10 @@
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>301</v>
+        <v>82</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>302</v>
+        <v>111</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
@@ -6736,21 +6767,21 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>82</v>
@@ -6759,19 +6790,19 @@
         <v>82</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>305</v>
+        <v>115</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>306</v>
+        <v>116</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>307</v>
+        <v>117</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6809,31 +6840,31 @@
         <v>82</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>308</v>
+        <v>121</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>82</v>
@@ -6842,10 +6873,10 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>309</v>
+        <v>82</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>310</v>
+        <v>111</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -6856,10 +6887,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6882,24 +6913,26 @@
         <v>94</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>173</v>
+        <v>135</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>306</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>307</v>
+      </c>
       <c r="O37" t="s" s="2">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>82</v>
@@ -6941,7 +6974,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6962,10 +6995,10 @@
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
@@ -6976,10 +7009,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7005,15 +7038,15 @@
         <v>107</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="N38" s="2"/>
-      <c r="O38" t="s" s="2">
-        <v>324</v>
-      </c>
+        <v>316</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>82</v>
       </c>
@@ -7061,7 +7094,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -7082,10 +7115,10 @@
         <v>82</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
@@ -7094,12 +7127,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7107,13 +7140,13 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>82</v>
@@ -7122,26 +7155,24 @@
         <v>94</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>330</v>
+        <v>173</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>333</v>
-      </c>
+        <v>324</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q39" s="2"/>
       <c r="R39" t="s" s="2">
-        <v>82</v>
+        <v>326</v>
       </c>
       <c r="S39" t="s" s="2">
         <v>82</v>
@@ -7183,7 +7214,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -7204,10 +7235,10 @@
         <v>82</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -7218,10 +7249,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7247,16 +7278,14 @@
         <v>107</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>342</v>
-      </c>
+        <v>333</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>82</v>
@@ -7305,7 +7334,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -7326,10 +7355,10 @@
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
@@ -7338,26 +7367,26 @@
         <v>82</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>348</v>
+        <v>82</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>82</v>
@@ -7366,19 +7395,19 @@
         <v>94</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>264</v>
+        <v>340</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
@@ -7403,13 +7432,13 @@
         <v>82</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>353</v>
+        <v>82</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>354</v>
+        <v>82</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>82</v>
@@ -7427,10 +7456,10 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
         <v>93</v>
@@ -7442,30 +7471,30 @@
         <v>105</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>355</v>
+        <v>82</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>356</v>
+        <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>357</v>
+        <v>346</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>358</v>
+        <v>347</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>359</v>
+        <v>82</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>360</v>
+        <v>82</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>361</v>
+        <v>348</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>361</v>
+        <v>349</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7485,19 +7514,23 @@
         <v>82</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K42" t="s" s="2">
         <v>107</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>108</v>
+        <v>350</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
+        <v>351</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>353</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
       </c>
@@ -7545,7 +7578,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>110</v>
+        <v>354</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7557,7 +7590,7 @@
         <v>82</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>82</v>
@@ -7566,10 +7599,10 @@
         <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>82</v>
+        <v>355</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>111</v>
+        <v>356</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -7578,46 +7611,48 @@
         <v>82</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>113</v>
+        <v>358</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>114</v>
+        <v>274</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>115</v>
+        <v>359</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>116</v>
+        <v>360</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O43" s="2"/>
+        <v>361</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>362</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
       </c>
@@ -7641,69 +7676,69 @@
         <v>82</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>82</v>
+        <v>363</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>82</v>
+        <v>364</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>121</v>
+        <v>357</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>82</v>
+        <v>365</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>82</v>
+        <v>366</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>82</v>
+        <v>367</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>111</v>
+        <v>368</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>82</v>
+        <v>369</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>82</v>
+        <v>370</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7711,11 +7746,11 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G44" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="G44" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="H44" t="s" s="2">
         <v>82</v>
       </c>
@@ -7723,23 +7758,19 @@
         <v>82</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>151</v>
+        <v>107</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>282</v>
+        <v>108</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>285</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>82</v>
       </c>
@@ -7775,29 +7806,31 @@
         <v>82</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="AC44" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>286</v>
+        <v>110</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>82</v>
@@ -7806,10 +7839,10 @@
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>287</v>
+        <v>82</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>288</v>
+        <v>111</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7820,23 +7853,21 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="C45" t="s" s="2">
-        <v>366</v>
-      </c>
+        <v>372</v>
+      </c>
+      <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>82</v>
@@ -7845,23 +7876,21 @@
         <v>82</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>151</v>
+        <v>114</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>282</v>
+        <v>115</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>283</v>
+        <v>116</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>285</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>82</v>
       </c>
@@ -7897,19 +7926,19 @@
         <v>82</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>286</v>
+        <v>121</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7921,7 +7950,7 @@
         <v>82</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>82</v>
@@ -7930,10 +7959,10 @@
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>287</v>
+        <v>82</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>288</v>
+        <v>111</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
@@ -7944,10 +7973,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7955,10 +7984,10 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>82</v>
@@ -7967,19 +7996,23 @@
         <v>82</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>107</v>
+        <v>151</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>108</v>
+        <v>292</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
+        <v>293</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>295</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>82</v>
       </c>
@@ -8015,31 +8048,29 @@
         <v>82</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC46" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>374</v>
+      </c>
+      <c r="AC46" s="2"/>
       <c r="AD46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>110</v>
+        <v>296</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>82</v>
@@ -8048,10 +8079,10 @@
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>82</v>
+        <v>297</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>111</v>
+        <v>298</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
@@ -8062,21 +8093,23 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="C47" s="2"/>
+        <v>373</v>
+      </c>
+      <c r="C47" t="s" s="2">
+        <v>376</v>
+      </c>
       <c r="D47" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>82</v>
@@ -8085,21 +8118,23 @@
         <v>82</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>114</v>
+        <v>151</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>115</v>
+        <v>292</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>116</v>
+        <v>293</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O47" s="2"/>
+        <v>294</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>295</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>82</v>
       </c>
@@ -8135,19 +8170,19 @@
         <v>82</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>121</v>
+        <v>296</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -8159,7 +8194,7 @@
         <v>82</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>82</v>
@@ -8168,10 +8203,10 @@
         <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>82</v>
+        <v>297</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>111</v>
+        <v>298</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
@@ -8182,10 +8217,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8193,7 +8228,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>93</v>
@@ -8205,29 +8240,25 @@
         <v>82</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>295</v>
+        <v>108</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>298</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
-        <v>373</v>
+        <v>82</v>
       </c>
       <c r="S48" t="s" s="2">
         <v>82</v>
@@ -8269,7 +8300,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>300</v>
+        <v>110</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8281,7 +8312,7 @@
         <v>82</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>82</v>
@@ -8290,10 +8321,10 @@
         <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>301</v>
+        <v>82</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>302</v>
+        <v>111</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
@@ -8304,21 +8335,21 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>82</v>
@@ -8327,19 +8358,19 @@
         <v>82</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>305</v>
+        <v>115</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>306</v>
+        <v>116</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>307</v>
+        <v>117</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8377,31 +8408,31 @@
         <v>82</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>308</v>
+        <v>121</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>82</v>
@@ -8410,10 +8441,10 @@
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>309</v>
+        <v>82</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>310</v>
+        <v>111</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -8424,10 +8455,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8450,24 +8481,26 @@
         <v>94</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>173</v>
+        <v>135</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>306</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>307</v>
+      </c>
       <c r="O50" t="s" s="2">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q50" s="2"/>
       <c r="R50" t="s" s="2">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="S50" t="s" s="2">
         <v>82</v>
@@ -8509,7 +8542,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8530,10 +8563,10 @@
         <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -8544,10 +8577,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8573,15 +8606,15 @@
         <v>107</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="N51" s="2"/>
-      <c r="O51" t="s" s="2">
-        <v>324</v>
-      </c>
+        <v>316</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>82</v>
       </c>
@@ -8629,7 +8662,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8650,10 +8683,10 @@
         <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8664,10 +8697,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8675,7 +8708,7 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>93</v>
@@ -8690,26 +8723,24 @@
         <v>94</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>330</v>
+        <v>173</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>333</v>
-      </c>
+        <v>324</v>
+      </c>
+      <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q52" s="2"/>
       <c r="R52" t="s" s="2">
-        <v>82</v>
+        <v>388</v>
       </c>
       <c r="S52" t="s" s="2">
         <v>82</v>
@@ -8751,7 +8782,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8772,10 +8803,10 @@
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8786,10 +8817,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8815,16 +8846,14 @@
         <v>107</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>342</v>
-      </c>
+        <v>333</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>82</v>
@@ -8873,7 +8902,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8894,10 +8923,10 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
@@ -8906,12 +8935,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8919,13 +8948,13 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>82</v>
@@ -8934,19 +8963,19 @@
         <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>385</v>
+        <v>340</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>386</v>
+        <v>341</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>387</v>
+        <v>342</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>388</v>
+        <v>343</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>389</v>
+        <v>344</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -8995,7 +9024,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>384</v>
+        <v>345</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -9010,19 +9039,19 @@
         <v>105</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>390</v>
+        <v>82</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>391</v>
+        <v>346</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>392</v>
+        <v>347</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>393</v>
+        <v>82</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>82</v>
@@ -9030,10 +9059,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9044,7 +9073,7 @@
         <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>82</v>
@@ -9056,18 +9085,20 @@
         <v>94</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>395</v>
+        <v>107</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>396</v>
+        <v>350</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>397</v>
+        <v>351</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="O55" s="2"/>
+        <v>352</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>353</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
       </c>
@@ -9115,13 +9146,13 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>394</v>
+        <v>354</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>82</v>
@@ -9136,38 +9167,38 @@
         <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>399</v>
+        <v>356</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>393</v>
+        <v>82</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>401</v>
+        <v>82</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G56" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>82</v>
@@ -9176,19 +9207,19 @@
         <v>94</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>82</v>
@@ -9237,7 +9268,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -9252,44 +9283,44 @@
         <v>105</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>412</v>
+        <v>82</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>82</v>
@@ -9298,20 +9329,18 @@
         <v>94</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>417</v>
-      </c>
+        <v>408</v>
+      </c>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>82</v>
       </c>
@@ -9359,34 +9388,34 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>418</v>
+        <v>82</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>419</v>
+        <v>105</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>420</v>
+        <v>82</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>421</v>
+        <v>367</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>422</v>
+        <v>409</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>423</v>
+        <v>403</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>82</v>
@@ -9394,14 +9423,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>82</v>
+        <v>411</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -9420,18 +9449,20 @@
         <v>94</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>129</v>
+        <v>412</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>425</v>
+        <v>413</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>426</v>
+        <v>414</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="O58" s="2"/>
+        <v>415</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>416</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>82</v>
       </c>
@@ -9479,7 +9510,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9494,44 +9525,44 @@
         <v>105</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>82</v>
+        <v>417</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>428</v>
+        <v>418</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="59" hidden="true">
+    <row r="59">
       <c r="A59" t="s" s="2">
-        <v>431</v>
+        <v>421</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>431</v>
+        <v>421</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>82</v>
+        <v>422</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>82</v>
@@ -9540,17 +9571,19 @@
         <v>94</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>432</v>
+        <v>423</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="N59" s="2"/>
+        <v>425</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>426</v>
+      </c>
       <c r="O59" t="s" s="2">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>82</v>
@@ -9599,34 +9632,34 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM59" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="AG59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ59" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK59" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="AL59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>437</v>
-      </c>
       <c r="AN59" t="s" s="2">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>82</v>
@@ -9634,10 +9667,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9651,7 +9684,7 @@
         <v>93</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>82</v>
@@ -9660,20 +9693,18 @@
         <v>94</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>441</v>
+        <v>129</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>442</v>
+        <v>435</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>444</v>
-      </c>
+        <v>437</v>
+      </c>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>82</v>
       </c>
@@ -9709,17 +9740,19 @@
         <v>82</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="AC60" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>446</v>
+        <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9728,7 +9761,7 @@
         <v>93</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>447</v>
+        <v>82</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>105</v>
@@ -9737,31 +9770,29 @@
         <v>82</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>448</v>
+        <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>449</v>
+        <v>438</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>450</v>
+        <v>439</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>82</v>
+        <v>440</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>451</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>452</v>
+        <v>441</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="C61" t="s" s="2">
-        <v>453</v>
-      </c>
+        <v>441</v>
+      </c>
+      <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
         <v>82</v>
       </c>
@@ -9770,10 +9801,10 @@
         <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>82</v>
@@ -9782,19 +9813,17 @@
         <v>94</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>443</v>
-      </c>
+        <v>444</v>
+      </c>
+      <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -9843,45 +9872,45 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>447</v>
+        <v>82</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>82</v>
+        <v>446</v>
       </c>
       <c r="AL61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AN61" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="AM61" t="s" s="2">
+      <c r="AO61" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="AN61" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AP61" t="s" s="2">
-        <v>451</v>
+        <v>82</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9895,25 +9924,29 @@
         <v>93</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>107</v>
+        <v>451</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>108</v>
+        <v>452</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
+        <v>452</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>454</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>82</v>
       </c>
@@ -9949,19 +9982,17 @@
         <v>82</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC62" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>455</v>
+      </c>
+      <c r="AC62" s="2"/>
       <c r="AD62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>82</v>
+        <v>456</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>110</v>
+        <v>450</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9970,70 +10001,74 @@
         <v>93</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>82</v>
+        <v>457</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>82</v>
+        <v>458</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>82</v>
+        <v>459</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>111</v>
+        <v>460</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>82</v>
+        <v>461</v>
       </c>
     </row>
-    <row r="63" hidden="true">
+    <row r="63">
       <c r="A63" t="s" s="2">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="C63" s="2"/>
+        <v>450</v>
+      </c>
+      <c r="C63" t="s" s="2">
+        <v>463</v>
+      </c>
       <c r="D63" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>114</v>
+        <v>451</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>115</v>
+        <v>452</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>116</v>
+        <v>452</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O63" s="2"/>
+        <v>453</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>454</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>82</v>
       </c>
@@ -10069,57 +10104,57 @@
         <v>82</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC63" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>121</v>
+        <v>450</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>82</v>
+        <v>457</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>82</v>
+        <v>458</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>82</v>
+        <v>459</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>111</v>
+        <v>460</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>82</v>
+        <v>461</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10127,35 +10162,31 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>460</v>
+        <v>107</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>461</v>
+        <v>108</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>464</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>82</v>
       </c>
@@ -10203,7 +10234,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>465</v>
+        <v>110</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -10215,7 +10246,7 @@
         <v>82</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>82</v>
@@ -10224,10 +10255,10 @@
         <v>82</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>466</v>
+        <v>82</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>467</v>
+        <v>111</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>
@@ -10238,50 +10269,48 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>173</v>
+        <v>114</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>470</v>
+        <v>115</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="N65" s="2"/>
-      <c r="O65" t="s" s="2">
-        <v>472</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q65" t="s" s="2">
-        <v>473</v>
-      </c>
+      <c r="Q65" s="2"/>
       <c r="R65" t="s" s="2">
         <v>82</v>
       </c>
@@ -10301,43 +10330,43 @@
         <v>82</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>256</v>
+        <v>82</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>474</v>
+        <v>82</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>475</v>
+        <v>82</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB65" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC65" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>476</v>
+        <v>121</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>82</v>
@@ -10346,10 +10375,10 @@
         <v>82</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>477</v>
+        <v>82</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>478</v>
+        <v>111</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
@@ -10360,10 +10389,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>479</v>
+        <v>468</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>480</v>
+        <v>469</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10386,17 +10415,19 @@
         <v>94</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>107</v>
+        <v>470</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>481</v>
+        <v>471</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="N66" s="2"/>
+        <v>472</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>473</v>
+      </c>
       <c r="O66" t="s" s="2">
-        <v>483</v>
+        <v>474</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>82</v>
@@ -10445,7 +10476,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>484</v>
+        <v>475</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10466,10 +10497,10 @@
         <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>486</v>
+        <v>477</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>82</v>
@@ -10478,12 +10509,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>487</v>
+        <v>478</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>488</v>
+        <v>479</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10491,39 +10522,41 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G67" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I67" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="I67" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="J67" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>489</v>
+        <v>480</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>490</v>
+        <v>481</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>491</v>
+        <v>482</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q67" s="2"/>
+      <c r="Q67" t="s" s="2">
+        <v>483</v>
+      </c>
       <c r="R67" t="s" s="2">
-        <v>492</v>
+        <v>82</v>
       </c>
       <c r="S67" t="s" s="2">
         <v>82</v>
@@ -10541,13 +10574,13 @@
         <v>82</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>82</v>
+        <v>266</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>82</v>
+        <v>484</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>82</v>
+        <v>485</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>82</v>
@@ -10565,7 +10598,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10574,7 +10607,7 @@
         <v>93</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>494</v>
+        <v>82</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>105</v>
@@ -10586,10 +10619,10 @@
         <v>82</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>82</v>
@@ -10600,10 +10633,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10626,26 +10659,24 @@
         <v>94</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>173</v>
+        <v>107</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>499</v>
-      </c>
+        <v>492</v>
+      </c>
+      <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q68" s="2"/>
       <c r="R68" t="s" s="2">
-        <v>501</v>
+        <v>82</v>
       </c>
       <c r="S68" t="s" s="2">
         <v>82</v>
@@ -10687,7 +10718,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>502</v>
+        <v>494</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10708,10 +10739,10 @@
         <v>82</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>485</v>
+        <v>495</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>503</v>
+        <v>496</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
@@ -10722,10 +10753,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10733,7 +10764,7 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G69" t="s" s="2">
         <v>93</v>
@@ -10745,29 +10776,27 @@
         <v>82</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>264</v>
+        <v>135</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>507</v>
-      </c>
+        <v>500</v>
+      </c>
+      <c r="N69" s="2"/>
       <c r="O69" t="s" s="2">
-        <v>508</v>
+        <v>501</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q69" s="2"/>
       <c r="R69" t="s" s="2">
-        <v>82</v>
+        <v>502</v>
       </c>
       <c r="S69" t="s" s="2">
         <v>82</v>
@@ -10785,13 +10814,13 @@
         <v>82</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>509</v>
+        <v>82</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>510</v>
+        <v>82</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>82</v>
@@ -10809,7 +10838,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10818,7 +10847,7 @@
         <v>93</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>105</v>
@@ -10830,10 +10859,10 @@
         <v>82</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>196</v>
+        <v>495</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
@@ -10842,12 +10871,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="70" hidden="true">
+    <row r="70">
       <c r="A70" t="s" s="2">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10855,37 +10884,41 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G70" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>107</v>
+        <v>173</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>108</v>
+        <v>508</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N70" s="2"/>
-      <c r="O70" s="2"/>
+        <v>508</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="O70" t="s" s="2">
+        <v>510</v>
+      </c>
       <c r="P70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q70" s="2"/>
       <c r="R70" t="s" s="2">
-        <v>82</v>
+        <v>511</v>
       </c>
       <c r="S70" t="s" s="2">
         <v>82</v>
@@ -10927,7 +10960,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>110</v>
+        <v>512</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10939,7 +10972,7 @@
         <v>82</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>82</v>
@@ -10948,10 +10981,10 @@
         <v>82</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>82</v>
+        <v>495</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>111</v>
+        <v>513</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>82</v>
@@ -10960,7 +10993,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="71" hidden="true">
+    <row r="71">
       <c r="A71" t="s" s="2">
         <v>514</v>
       </c>
@@ -10969,17 +11002,17 @@
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>82</v>
@@ -10988,18 +11021,20 @@
         <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>114</v>
+        <v>274</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>115</v>
+        <v>515</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>116</v>
+        <v>516</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O71" s="2"/>
+        <v>517</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>518</v>
+      </c>
       <c r="P71" t="s" s="2">
         <v>82</v>
       </c>
@@ -11023,43 +11058,43 @@
         <v>82</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>82</v>
+        <v>519</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>82</v>
+        <v>520</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB71" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC71" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>121</v>
+        <v>514</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>82</v>
+        <v>521</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>82</v>
@@ -11068,10 +11103,10 @@
         <v>82</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>82</v>
+        <v>196</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>111</v>
+        <v>522</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
@@ -11082,10 +11117,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11096,7 +11131,7 @@
         <v>80</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>82</v>
@@ -11105,23 +11140,19 @@
         <v>82</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>151</v>
+        <v>107</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>282</v>
+        <v>108</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>285</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N72" s="2"/>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>82</v>
       </c>
@@ -11169,19 +11200,19 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>286</v>
+        <v>110</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>82</v>
@@ -11190,10 +11221,10 @@
         <v>82</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>287</v>
+        <v>82</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>288</v>
+        <v>111</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>82</v>
@@ -11204,21 +11235,21 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>516</v>
+        <v>524</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>516</v>
+        <v>524</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>82</v>
@@ -11230,15 +11261,17 @@
         <v>82</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N73" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>82</v>
@@ -11275,31 +11308,31 @@
         <v>82</v>
       </c>
       <c r="AB73" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC73" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>82</v>
@@ -11322,14 +11355,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -11345,21 +11378,23 @@
         <v>82</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>114</v>
+        <v>151</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>115</v>
+        <v>292</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>116</v>
+        <v>293</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O74" s="2"/>
+        <v>294</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>295</v>
+      </c>
       <c r="P74" t="s" s="2">
         <v>82</v>
       </c>
@@ -11395,19 +11430,19 @@
         <v>82</v>
       </c>
       <c r="AB74" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC74" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>121</v>
+        <v>296</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11419,7 +11454,7 @@
         <v>82</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>82</v>
@@ -11428,10 +11463,10 @@
         <v>82</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>82</v>
+        <v>297</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>111</v>
+        <v>298</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
@@ -11442,10 +11477,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11453,7 +11488,7 @@
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G75" t="s" s="2">
         <v>93</v>
@@ -11465,23 +11500,19 @@
         <v>82</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>295</v>
+        <v>108</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>298</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N75" s="2"/>
+      <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>82</v>
       </c>
@@ -11529,7 +11560,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>300</v>
+        <v>110</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11541,7 +11572,7 @@
         <v>82</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>82</v>
@@ -11550,10 +11581,10 @@
         <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>301</v>
+        <v>82</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>302</v>
+        <v>111</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>82</v>
@@ -11564,21 +11595,21 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>82</v>
@@ -11587,19 +11618,19 @@
         <v>82</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>305</v>
+        <v>115</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>306</v>
+        <v>116</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>307</v>
+        <v>117</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11637,31 +11668,31 @@
         <v>82</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC76" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>308</v>
+        <v>121</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>82</v>
@@ -11670,10 +11701,10 @@
         <v>82</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>309</v>
+        <v>82</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>310</v>
+        <v>111</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>82</v>
@@ -11684,10 +11715,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11710,17 +11741,19 @@
         <v>94</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>173</v>
+        <v>135</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="N77" s="2"/>
+        <v>306</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>307</v>
+      </c>
       <c r="O77" t="s" s="2">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>82</v>
@@ -11769,7 +11802,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11790,10 +11823,10 @@
         <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>82</v>
@@ -11804,10 +11837,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11833,15 +11866,15 @@
         <v>107</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="N78" s="2"/>
-      <c r="O78" t="s" s="2">
-        <v>324</v>
-      </c>
+        <v>316</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>82</v>
       </c>
@@ -11889,7 +11922,7 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11910,10 +11943,10 @@
         <v>82</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>82</v>
@@ -11924,10 +11957,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11935,7 +11968,7 @@
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G79" t="s" s="2">
         <v>93</v>
@@ -11950,19 +11983,17 @@
         <v>94</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>330</v>
+        <v>173</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>333</v>
-      </c>
+        <v>324</v>
+      </c>
+      <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>82</v>
@@ -12011,7 +12042,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -12032,10 +12063,10 @@
         <v>82</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>82</v>
@@ -12046,10 +12077,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12075,16 +12106,14 @@
         <v>107</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>342</v>
-      </c>
+        <v>333</v>
+      </c>
+      <c r="N80" s="2"/>
       <c r="O80" t="s" s="2">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>82</v>
@@ -12133,7 +12162,7 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -12154,10 +12183,10 @@
         <v>82</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>82</v>
@@ -12168,21 +12197,21 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>525</v>
+        <v>82</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>82</v>
@@ -12191,22 +12220,22 @@
         <v>82</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>264</v>
+        <v>340</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>526</v>
+        <v>341</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>527</v>
+        <v>342</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>528</v>
+        <v>343</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>529</v>
+        <v>344</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>82</v>
@@ -12231,11 +12260,13 @@
         <v>82</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="Y81" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z81" t="s" s="2">
-        <v>530</v>
+        <v>82</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>82</v>
@@ -12253,13 +12284,13 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>524</v>
+        <v>345</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>82</v>
@@ -12271,27 +12302,27 @@
         <v>82</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>531</v>
+        <v>82</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>532</v>
+        <v>346</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>533</v>
+        <v>347</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>534</v>
+        <v>82</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12302,7 +12333,7 @@
         <v>80</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>82</v>
@@ -12311,22 +12342,22 @@
         <v>82</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>536</v>
+        <v>107</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>537</v>
+        <v>350</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>538</v>
+        <v>351</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>539</v>
+        <v>352</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>540</v>
+        <v>353</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>82</v>
@@ -12375,13 +12406,13 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>535</v>
+        <v>354</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>82</v>
@@ -12396,10 +12427,10 @@
         <v>82</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>541</v>
+        <v>355</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>542</v>
+        <v>356</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>82</v>
@@ -12410,21 +12441,21 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>543</v>
+        <v>534</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>543</v>
+        <v>534</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>82</v>
+        <v>535</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>82</v>
@@ -12436,18 +12467,20 @@
         <v>82</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="O83" s="2"/>
+        <v>538</v>
+      </c>
+      <c r="O83" t="s" s="2">
+        <v>539</v>
+      </c>
       <c r="P83" t="s" s="2">
         <v>82</v>
       </c>
@@ -12471,11 +12504,11 @@
         <v>82</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="Y83" s="2"/>
       <c r="Z83" t="s" s="2">
-        <v>547</v>
+        <v>540</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>82</v>
@@ -12493,13 +12526,13 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>543</v>
+        <v>534</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>82</v>
@@ -12511,27 +12544,27 @@
         <v>82</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>548</v>
+        <v>541</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>549</v>
+        <v>542</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>550</v>
+        <v>543</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>551</v>
+        <v>544</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>552</v>
+        <v>545</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>552</v>
+        <v>545</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12542,7 +12575,7 @@
         <v>80</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>82</v>
@@ -12554,16 +12587,20 @@
         <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>107</v>
+        <v>546</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>108</v>
+        <v>547</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N84" s="2"/>
-      <c r="O84" s="2"/>
+        <v>548</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="O84" t="s" s="2">
+        <v>550</v>
+      </c>
       <c r="P84" t="s" s="2">
         <v>82</v>
       </c>
@@ -12611,19 +12648,19 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>110</v>
+        <v>545</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>82</v>
@@ -12632,10 +12669,10 @@
         <v>82</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>82</v>
+        <v>551</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>111</v>
+        <v>552</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>82</v>
@@ -12653,14 +12690,14 @@
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>82</v>
@@ -12672,16 +12709,16 @@
         <v>82</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>114</v>
+        <v>274</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>115</v>
+        <v>554</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>116</v>
+        <v>555</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>117</v>
+        <v>556</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12707,69 +12744,67 @@
         <v>82</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y85" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="Y85" s="2"/>
       <c r="Z85" t="s" s="2">
-        <v>82</v>
+        <v>557</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB85" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC85" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE85" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>121</v>
+        <v>553</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>82</v>
+        <v>558</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>82</v>
+        <v>559</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>111</v>
+        <v>560</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>82</v>
+        <v>561</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>554</v>
+        <v>562</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>554</v>
+        <v>562</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12780,7 +12815,7 @@
         <v>80</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>82</v>
@@ -12789,23 +12824,19 @@
         <v>82</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>151</v>
+        <v>107</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>282</v>
+        <v>108</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>285</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N86" s="2"/>
+      <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>82</v>
       </c>
@@ -12829,11 +12860,13 @@
         <v>82</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="Y86" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z86" t="s" s="2">
-        <v>555</v>
+        <v>82</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>82</v>
@@ -12851,19 +12884,19 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>286</v>
+        <v>110</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>82</v>
@@ -12872,10 +12905,10 @@
         <v>82</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>287</v>
+        <v>82</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>288</v>
+        <v>111</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>82</v>
@@ -12886,21 +12919,21 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>556</v>
+        <v>563</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>556</v>
+        <v>563</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>82</v>
@@ -12909,23 +12942,21 @@
         <v>82</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>340</v>
+        <v>115</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>341</v>
+        <v>116</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>343</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>82</v>
       </c>
@@ -12961,31 +12992,31 @@
         <v>82</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC87" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>344</v>
+        <v>121</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>82</v>
@@ -12994,10 +13025,10 @@
         <v>82</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>345</v>
+        <v>82</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>346</v>
+        <v>111</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>82</v>
@@ -13006,12 +13037,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13022,31 +13053,31 @@
         <v>80</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J88" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="I88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J88" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K88" t="s" s="2">
-        <v>264</v>
+        <v>151</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>558</v>
+        <v>292</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>559</v>
+        <v>293</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>560</v>
+        <v>294</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>561</v>
+        <v>295</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>82</v>
@@ -13071,11 +13102,11 @@
         <v>82</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="Y88" s="2"/>
       <c r="Z88" t="s" s="2">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>82</v>
@@ -13093,13 +13124,13 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>557</v>
+        <v>296</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>82</v>
@@ -13114,10 +13145,10 @@
         <v>82</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>563</v>
+        <v>297</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>564</v>
+        <v>298</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>82</v>
@@ -13128,10 +13159,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13151,19 +13182,23 @@
         <v>82</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K89" t="s" s="2">
         <v>107</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>108</v>
+        <v>350</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N89" s="2"/>
-      <c r="O89" s="2"/>
+        <v>351</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="O89" t="s" s="2">
+        <v>353</v>
+      </c>
       <c r="P89" t="s" s="2">
         <v>82</v>
       </c>
@@ -13211,7 +13246,7 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>110</v>
+        <v>354</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -13223,7 +13258,7 @@
         <v>82</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>82</v>
@@ -13232,10 +13267,10 @@
         <v>82</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>82</v>
+        <v>355</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>111</v>
+        <v>356</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>82</v>
@@ -13244,26 +13279,26 @@
         <v>82</v>
       </c>
     </row>
-    <row r="90" hidden="true">
+    <row r="90">
       <c r="A90" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H90" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I90" t="s" s="2">
         <v>82</v>
@@ -13272,18 +13307,20 @@
         <v>82</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>114</v>
+        <v>274</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>115</v>
+        <v>568</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>116</v>
+        <v>569</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O90" s="2"/>
+        <v>570</v>
+      </c>
+      <c r="O90" t="s" s="2">
+        <v>571</v>
+      </c>
       <c r="P90" t="s" s="2">
         <v>82</v>
       </c>
@@ -13307,43 +13344,41 @@
         <v>82</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y90" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="Y90" s="2"/>
       <c r="Z90" t="s" s="2">
-        <v>82</v>
+        <v>572</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB90" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC90" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE90" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>121</v>
+        <v>567</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>82</v>
@@ -13352,10 +13387,10 @@
         <v>82</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>82</v>
+        <v>573</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>111</v>
+        <v>574</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>82</v>
@@ -13366,10 +13401,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13380,7 +13415,7 @@
         <v>80</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>82</v>
@@ -13389,23 +13424,19 @@
         <v>82</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>151</v>
+        <v>107</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>282</v>
+        <v>108</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>285</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N91" s="2"/>
+      <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>82</v>
       </c>
@@ -13429,11 +13460,13 @@
         <v>82</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="Y91" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z91" t="s" s="2">
-        <v>568</v>
+        <v>82</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>82</v>
@@ -13451,19 +13484,19 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>286</v>
+        <v>110</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>82</v>
@@ -13472,10 +13505,10 @@
         <v>82</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>287</v>
+        <v>82</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>288</v>
+        <v>111</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>82</v>
@@ -13486,21 +13519,21 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>569</v>
+        <v>576</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>569</v>
+        <v>576</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>82</v>
@@ -13509,23 +13542,21 @@
         <v>82</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>340</v>
+        <v>115</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>341</v>
+        <v>116</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="O92" t="s" s="2">
-        <v>343</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>82</v>
       </c>
@@ -13561,31 +13592,31 @@
         <v>82</v>
       </c>
       <c r="AB92" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC92" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE92" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>344</v>
+        <v>121</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>82</v>
@@ -13594,10 +13625,10 @@
         <v>82</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>345</v>
+        <v>82</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>346</v>
+        <v>111</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>82</v>
@@ -13608,10 +13639,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>570</v>
+        <v>577</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>570</v>
+        <v>577</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13622,7 +13653,7 @@
         <v>80</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>82</v>
@@ -13631,21 +13662,23 @@
         <v>82</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>571</v>
+        <v>151</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>572</v>
+        <v>292</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>573</v>
+        <v>293</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="O93" s="2"/>
+        <v>294</v>
+      </c>
+      <c r="O93" t="s" s="2">
+        <v>295</v>
+      </c>
       <c r="P93" t="s" s="2">
         <v>82</v>
       </c>
@@ -13669,13 +13702,11 @@
         <v>82</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y93" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="Y93" s="2"/>
       <c r="Z93" t="s" s="2">
-        <v>82</v>
+        <v>578</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>82</v>
@@ -13693,13 +13724,13 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>570</v>
+        <v>296</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>82</v>
@@ -13711,22 +13742,22 @@
         <v>82</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>575</v>
+        <v>82</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>576</v>
+        <v>297</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>577</v>
+        <v>298</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>578</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
         <v>579</v>
       </c>
@@ -13745,27 +13776,29 @@
         <v>93</v>
       </c>
       <c r="H94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J94" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="I94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J94" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K94" t="s" s="2">
-        <v>580</v>
+        <v>107</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>581</v>
+        <v>350</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>582</v>
+        <v>351</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="O94" s="2"/>
+        <v>352</v>
+      </c>
+      <c r="O94" t="s" s="2">
+        <v>353</v>
+      </c>
       <c r="P94" t="s" s="2">
         <v>82</v>
       </c>
@@ -13813,7 +13846,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>579</v>
+        <v>354</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13831,27 +13864,27 @@
         <v>82</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>584</v>
+        <v>82</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>585</v>
+        <v>355</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>586</v>
+        <v>356</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>587</v>
+        <v>82</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>588</v>
+        <v>580</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>588</v>
+        <v>580</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13862,7 +13895,7 @@
         <v>80</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>82</v>
@@ -13874,20 +13907,18 @@
         <v>82</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>589</v>
+        <v>581</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>590</v>
+        <v>582</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>591</v>
+        <v>583</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="O95" t="s" s="2">
-        <v>593</v>
-      </c>
+        <v>584</v>
+      </c>
+      <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>82</v>
       </c>
@@ -13935,45 +13966,45 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="AG95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH95" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ95" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL95" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="AM95" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="AN95" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="AO95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP95" t="s" s="2">
         <v>588</v>
       </c>
-      <c r="AG95" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ95" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="AK95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM95" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="AN95" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="AO95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP95" t="s" s="2">
-        <v>82</v>
-      </c>
     </row>
-    <row r="96" hidden="true">
+    <row r="96">
       <c r="A96" t="s" s="2">
-        <v>597</v>
+        <v>589</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>597</v>
+        <v>589</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13987,7 +14018,7 @@
         <v>93</v>
       </c>
       <c r="H96" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I96" t="s" s="2">
         <v>82</v>
@@ -13996,15 +14027,17 @@
         <v>82</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>107</v>
+        <v>590</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>108</v>
+        <v>591</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N96" s="2"/>
+        <v>592</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>593</v>
+      </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>82</v>
@@ -14053,7 +14086,7 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>110</v>
+        <v>589</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -14065,25 +14098,25 @@
         <v>82</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>82</v>
+        <v>594</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>82</v>
+        <v>595</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>111</v>
+        <v>596</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP96" t="s" s="2">
-        <v>82</v>
+        <v>597</v>
       </c>
     </row>
     <row r="97" hidden="true">
@@ -14095,7 +14128,7 @@
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -14114,18 +14147,20 @@
         <v>82</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>114</v>
+        <v>599</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>115</v>
+        <v>600</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>116</v>
+        <v>601</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O97" s="2"/>
+        <v>602</v>
+      </c>
+      <c r="O97" t="s" s="2">
+        <v>603</v>
+      </c>
       <c r="P97" t="s" s="2">
         <v>82</v>
       </c>
@@ -14173,7 +14208,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>121</v>
+        <v>598</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -14185,7 +14220,7 @@
         <v>82</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>122</v>
+        <v>604</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>82</v>
@@ -14194,10 +14229,10 @@
         <v>82</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>82</v>
+        <v>605</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>111</v>
+        <v>606</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>82</v>
@@ -14208,46 +14243,42 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>600</v>
+        <v>82</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I98" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>601</v>
+        <v>108</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O98" t="s" s="2">
-        <v>222</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N98" s="2"/>
+      <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>82</v>
       </c>
@@ -14295,19 +14326,19 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>603</v>
+        <v>110</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>82</v>
@@ -14319,7 +14350,7 @@
         <v>82</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>196</v>
+        <v>111</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>82</v>
@@ -14330,21 +14361,21 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>82</v>
@@ -14356,15 +14387,17 @@
         <v>82</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>605</v>
+        <v>114</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>606</v>
+        <v>115</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="N99" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N99" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
         <v>82</v>
@@ -14413,19 +14446,19 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>604</v>
+        <v>121</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>608</v>
+        <v>82</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>82</v>
@@ -14434,10 +14467,10 @@
         <v>82</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>609</v>
+        <v>82</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>610</v>
+        <v>111</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>82</v>
@@ -14448,42 +14481,46 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>82</v>
+        <v>610</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I100" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>605</v>
+        <v>114</v>
       </c>
       <c r="L100" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="M100" t="s" s="2">
         <v>612</v>
       </c>
-      <c r="M100" t="s" s="2">
-        <v>613</v>
-      </c>
-      <c r="N100" s="2"/>
-      <c r="O100" s="2"/>
+      <c r="N100" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O100" t="s" s="2">
+        <v>232</v>
+      </c>
       <c r="P100" t="s" s="2">
         <v>82</v>
       </c>
@@ -14531,19 +14568,19 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>608</v>
+        <v>82</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>82</v>
@@ -14552,10 +14589,10 @@
         <v>82</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>609</v>
+        <v>82</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>614</v>
+        <v>196</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>82</v>
@@ -14566,10 +14603,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14592,7 +14629,7 @@
         <v>82</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>264</v>
+        <v>615</v>
       </c>
       <c r="L101" t="s" s="2">
         <v>616</v>
@@ -14600,12 +14637,8 @@
       <c r="M101" t="s" s="2">
         <v>617</v>
       </c>
-      <c r="N101" t="s" s="2">
-        <v>618</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>619</v>
-      </c>
+      <c r="N101" s="2"/>
+      <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>82</v>
       </c>
@@ -14629,13 +14662,13 @@
         <v>82</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>620</v>
+        <v>82</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>621</v>
+        <v>82</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>82</v>
@@ -14653,7 +14686,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14662,7 +14695,7 @@
         <v>93</v>
       </c>
       <c r="AI101" t="s" s="2">
-        <v>82</v>
+        <v>618</v>
       </c>
       <c r="AJ101" t="s" s="2">
         <v>105</v>
@@ -14671,13 +14704,13 @@
         <v>82</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>622</v>
+        <v>82</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>533</v>
+        <v>620</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>82</v>
@@ -14688,10 +14721,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14702,7 +14735,7 @@
         <v>80</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H102" t="s" s="2">
         <v>82</v>
@@ -14714,20 +14747,16 @@
         <v>82</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>264</v>
+        <v>615</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>627</v>
-      </c>
-      <c r="O102" t="s" s="2">
-        <v>628</v>
-      </c>
+        <v>623</v>
+      </c>
+      <c r="N102" s="2"/>
+      <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>82</v>
       </c>
@@ -14751,13 +14780,13 @@
         <v>82</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>163</v>
+        <v>82</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>629</v>
+        <v>82</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>630</v>
+        <v>82</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>82</v>
@@ -14775,16 +14804,16 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>82</v>
+        <v>618</v>
       </c>
       <c r="AJ102" t="s" s="2">
         <v>105</v>
@@ -14793,13 +14822,13 @@
         <v>82</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>622</v>
+        <v>82</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>533</v>
+        <v>624</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>82</v>
@@ -14810,10 +14839,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>631</v>
+        <v>625</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>631</v>
+        <v>625</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14836,17 +14865,19 @@
         <v>82</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>632</v>
+        <v>274</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>633</v>
+        <v>626</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="N103" s="2"/>
+        <v>627</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>628</v>
+      </c>
       <c r="O103" t="s" s="2">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>82</v>
@@ -14871,13 +14902,13 @@
         <v>82</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>82</v>
+        <v>630</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>82</v>
+        <v>631</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>82</v>
@@ -14895,7 +14926,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>631</v>
+        <v>625</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -14913,13 +14944,13 @@
         <v>82</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>82</v>
+        <v>632</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>82</v>
+        <v>633</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>636</v>
+        <v>543</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>82</v>
@@ -14930,10 +14961,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14944,7 +14975,7 @@
         <v>80</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H104" t="s" s="2">
         <v>82</v>
@@ -14956,16 +14987,20 @@
         <v>82</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>107</v>
+        <v>274</v>
       </c>
       <c r="L104" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="M104" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="O104" t="s" s="2">
         <v>638</v>
       </c>
-      <c r="M104" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="N104" s="2"/>
-      <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
         <v>82</v>
       </c>
@@ -14989,13 +15024,13 @@
         <v>82</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>82</v>
+        <v>639</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>82</v>
+        <v>640</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>82</v>
@@ -15013,13 +15048,13 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI104" t="s" s="2">
         <v>82</v>
@@ -15031,13 +15066,13 @@
         <v>82</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>82</v>
+        <v>632</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>609</v>
+        <v>633</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>640</v>
+        <v>543</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>82</v>
@@ -15062,7 +15097,7 @@
         <v>80</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>82</v>
@@ -15071,7 +15106,7 @@
         <v>82</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K105" t="s" s="2">
         <v>642</v>
@@ -15082,10 +15117,10 @@
       <c r="M105" t="s" s="2">
         <v>644</v>
       </c>
-      <c r="N105" t="s" s="2">
+      <c r="N105" s="2"/>
+      <c r="O105" t="s" s="2">
         <v>645</v>
       </c>
-      <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
         <v>82</v>
       </c>
@@ -15139,7 +15174,7 @@
         <v>80</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI105" t="s" s="2">
         <v>82</v>
@@ -15154,10 +15189,10 @@
         <v>82</v>
       </c>
       <c r="AM105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN105" t="s" s="2">
         <v>646</v>
-      </c>
-      <c r="AN105" t="s" s="2">
-        <v>647</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>82</v>
@@ -15168,10 +15203,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15182,7 +15217,7 @@
         <v>80</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>82</v>
@@ -15191,20 +15226,18 @@
         <v>82</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K106" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L106" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="M106" t="s" s="2">
         <v>649</v>
       </c>
-      <c r="L106" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>651</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>652</v>
-      </c>
+      <c r="N106" s="2"/>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
         <v>82</v>
@@ -15253,13 +15286,13 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>82</v>
@@ -15274,10 +15307,10 @@
         <v>82</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>646</v>
+        <v>619</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>82</v>
@@ -15286,12 +15319,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15305,7 +15338,7 @@
         <v>81</v>
       </c>
       <c r="H107" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I107" t="s" s="2">
         <v>82</v>
@@ -15314,20 +15347,18 @@
         <v>94</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>589</v>
+        <v>652</v>
       </c>
       <c r="L107" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="M107" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="N107" t="s" s="2">
         <v>655</v>
       </c>
-      <c r="M107" t="s" s="2">
-        <v>655</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>656</v>
-      </c>
-      <c r="O107" t="s" s="2">
-        <v>657</v>
-      </c>
+      <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
         <v>82</v>
       </c>
@@ -15375,7 +15406,7 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15387,7 +15418,7 @@
         <v>82</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>658</v>
+        <v>105</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>82</v>
@@ -15396,10 +15427,10 @@
         <v>82</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>82</v>
@@ -15410,10 +15441,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15424,7 +15455,7 @@
         <v>80</v>
       </c>
       <c r="G108" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H108" t="s" s="2">
         <v>82</v>
@@ -15433,18 +15464,20 @@
         <v>82</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>107</v>
+        <v>659</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>108</v>
+        <v>660</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N108" s="2"/>
+        <v>661</v>
+      </c>
+      <c r="N108" t="s" s="2">
+        <v>662</v>
+      </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
         <v>82</v>
@@ -15493,19 +15526,19 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>110</v>
+        <v>658</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH108" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI108" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK108" t="s" s="2">
         <v>82</v>
@@ -15514,10 +15547,10 @@
         <v>82</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>82</v>
+        <v>656</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>111</v>
+        <v>663</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>82</v>
@@ -15526,16 +15559,16 @@
         <v>82</v>
       </c>
     </row>
-    <row r="109" hidden="true">
+    <row r="109">
       <c r="A109" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
@@ -15545,27 +15578,29 @@
         <v>81</v>
       </c>
       <c r="H109" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I109" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>114</v>
+        <v>599</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>115</v>
+        <v>665</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>116</v>
+        <v>665</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O109" s="2"/>
+        <v>666</v>
+      </c>
+      <c r="O109" t="s" s="2">
+        <v>667</v>
+      </c>
       <c r="P109" t="s" s="2">
         <v>82</v>
       </c>
@@ -15613,7 +15648,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>121</v>
+        <v>664</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15625,7 +15660,7 @@
         <v>82</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>122</v>
+        <v>668</v>
       </c>
       <c r="AK109" t="s" s="2">
         <v>82</v>
@@ -15634,10 +15669,10 @@
         <v>82</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>82</v>
+        <v>669</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>111</v>
+        <v>670</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>82</v>
@@ -15648,46 +15683,42 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>663</v>
+        <v>671</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>663</v>
+        <v>671</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>600</v>
+        <v>82</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H110" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I110" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>601</v>
+        <v>108</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O110" t="s" s="2">
-        <v>222</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N110" s="2"/>
+      <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
         <v>82</v>
       </c>
@@ -15735,19 +15766,19 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>603</v>
+        <v>110</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI110" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK110" t="s" s="2">
         <v>82</v>
@@ -15759,7 +15790,7 @@
         <v>82</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>196</v>
+        <v>111</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>82</v>
@@ -15768,48 +15799,46 @@
         <v>82</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>664</v>
+        <v>672</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>664</v>
+        <v>672</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H111" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I111" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>264</v>
+        <v>114</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>665</v>
+        <v>115</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>666</v>
+        <v>116</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>667</v>
-      </c>
-      <c r="O111" t="s" s="2">
-        <v>668</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
         <v>82</v>
       </c>
@@ -15833,13 +15862,13 @@
         <v>82</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>353</v>
+        <v>82</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>354</v>
+        <v>82</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>82</v>
@@ -15857,80 +15886,80 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>664</v>
+        <v>121</v>
       </c>
       <c r="AG111" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI111" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK111" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>669</v>
+        <v>82</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>357</v>
+        <v>82</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>358</v>
+        <v>111</v>
       </c>
       <c r="AO111" t="s" s="2">
-        <v>359</v>
+        <v>82</v>
       </c>
       <c r="AP111" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>82</v>
+        <v>610</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I112" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="I112" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="J112" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>671</v>
+        <v>114</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>672</v>
+        <v>611</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>673</v>
+        <v>612</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>674</v>
+        <v>117</v>
       </c>
       <c r="O112" t="s" s="2">
-        <v>444</v>
+        <v>232</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>82</v>
@@ -15955,13 +15984,13 @@
         <v>82</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>675</v>
+        <v>82</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>676</v>
+        <v>82</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>82</v>
@@ -15979,45 +16008,45 @@
         <v>82</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>670</v>
+        <v>613</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI112" t="s" s="2">
-        <v>677</v>
+        <v>82</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK112" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>678</v>
+        <v>82</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>449</v>
+        <v>82</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>450</v>
+        <v>196</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP112" t="s" s="2">
-        <v>451</v>
+        <v>82</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16025,7 +16054,7 @@
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G113" t="s" s="2">
         <v>93</v>
@@ -16037,22 +16066,22 @@
         <v>82</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>682</v>
+        <v>677</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>508</v>
+        <v>678</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>82</v>
@@ -16080,10 +16109,10 @@
         <v>155</v>
       </c>
       <c r="Y113" t="s" s="2">
-        <v>509</v>
+        <v>363</v>
       </c>
       <c r="Z113" t="s" s="2">
-        <v>510</v>
+        <v>364</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>82</v>
@@ -16101,16 +16130,16 @@
         <v>82</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="AG113" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH113" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AI113" t="s" s="2">
-        <v>683</v>
+        <v>82</v>
       </c>
       <c r="AJ113" t="s" s="2">
         <v>105</v>
@@ -16119,62 +16148,62 @@
         <v>82</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>82</v>
+        <v>679</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>196</v>
+        <v>367</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>512</v>
+        <v>368</v>
       </c>
       <c r="AO113" t="s" s="2">
-        <v>82</v>
+        <v>369</v>
       </c>
       <c r="AP113" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="114" hidden="true">
+    <row r="114">
       <c r="A114" t="s" s="2">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
-        <v>525</v>
+        <v>82</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H114" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I114" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J114" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>264</v>
+        <v>681</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>526</v>
+        <v>682</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>527</v>
+        <v>683</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>528</v>
+        <v>684</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>529</v>
+        <v>454</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>82</v>
@@ -16205,7 +16234,7 @@
         <v>685</v>
       </c>
       <c r="Z114" t="s" s="2">
-        <v>530</v>
+        <v>686</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>82</v>
@@ -16223,16 +16252,16 @@
         <v>82</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI114" t="s" s="2">
-        <v>82</v>
+        <v>687</v>
       </c>
       <c r="AJ114" t="s" s="2">
         <v>105</v>
@@ -16241,27 +16270,27 @@
         <v>82</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>531</v>
+        <v>688</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>532</v>
+        <v>459</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>533</v>
+        <v>460</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP114" t="s" s="2">
-        <v>534</v>
+        <v>461</v>
       </c>
     </row>
-    <row r="115" hidden="true">
+    <row r="115">
       <c r="A115" t="s" s="2">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16272,10 +16301,10 @@
         <v>80</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H115" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I115" t="s" s="2">
         <v>82</v>
@@ -16284,19 +16313,19 @@
         <v>82</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>83</v>
+        <v>274</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>592</v>
+        <v>692</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>593</v>
+        <v>518</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>82</v>
@@ -16321,13 +16350,13 @@
         <v>82</v>
       </c>
       <c r="X115" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="Y115" t="s" s="2">
-        <v>82</v>
+        <v>519</v>
       </c>
       <c r="Z115" t="s" s="2">
-        <v>82</v>
+        <v>520</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>82</v>
@@ -16345,16 +16374,16 @@
         <v>82</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH115" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI115" t="s" s="2">
-        <v>82</v>
+        <v>693</v>
       </c>
       <c r="AJ115" t="s" s="2">
         <v>105</v>
@@ -16366,20 +16395,264 @@
         <v>82</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>595</v>
+        <v>196</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>596</v>
+        <v>522</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP115" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="116" hidden="true">
+      <c r="A116" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="B116" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="C116" s="2"/>
+      <c r="D116" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="E116" s="2"/>
+      <c r="F116" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K116" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="L116" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="M116" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="N116" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="O116" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="P116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q116" s="2"/>
+      <c r="R116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X116" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="Y116" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="Z116" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="AA116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF116" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="AG116" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ116" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL116" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="AM116" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="AN116" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="AO116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP116" t="s" s="2">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="117" hidden="true">
+      <c r="A117" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="B117" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="C117" s="2"/>
+      <c r="D117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E117" s="2"/>
+      <c r="F117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K117" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L117" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="M117" t="s" s="2">
+        <v>698</v>
+      </c>
+      <c r="N117" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="O117" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="P117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q117" s="2"/>
+      <c r="R117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF117" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="AG117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ117" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM117" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="AN117" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="AO117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP117" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP115">
+  <autoFilter ref="A1:AP117">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -16389,7 +16662,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI114">
+  <conditionalFormatting sqref="A2:AI116">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T08:51:58+00:00</t>
+    <t>2026-01-19T09:23:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:23:14+00:00</t>
+    <t>2026-01-19T09:39:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:39:10+00:00</t>
+    <t>2026-01-19T09:47:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:47:31+00:00</t>
+    <t>2026-01-19T09:54:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:54:18+00:00</t>
+    <t>2026-01-19T09:56:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:56:13+00:00</t>
+    <t>2026-01-19T10:07:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T10:07:50+00:00</t>
+    <t>2026-01-20T07:44:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T07:44:39+00:00</t>
+    <t>2026-01-20T09:11:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T09:11:57+00:00</t>
+    <t>2026-01-20T09:43:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T09:43:53+00:00</t>
+    <t>2026-01-20T09:47:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T09:47:48+00:00</t>
+    <t>2026-01-20T10:06:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T10:06:11+00:00</t>
+    <t>2026-01-20T11:11:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$117</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$116</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4509" uniqueCount="699">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4471" uniqueCount="694">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T11:11:06+00:00</t>
+    <t>2026-01-20T12:50:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -704,22 +704,6 @@
   <si>
     <t>Motif de la mesure
 Texte libre (ex. diabète, surpoids, hypercholestérolémie, risque cardiovasculaire, suivi, ...)</t>
-  </si>
-  <si>
-    <t>Observation.extension:MesOriginOfData</t>
-  </si>
-  <si>
-    <t>MesOriginOfData</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-origin-of-data}
-</t>
-  </si>
-  <si>
-    <t>Origine de la donnée</t>
-  </si>
-  <si>
-    <t>Extension pour tracer l'origine de la donnée issue d'un compte rendu de biologie (CR-Bio).</t>
   </si>
   <si>
     <t>Observation.extension:MesMomentOfMeasurement</t>
@@ -2513,7 +2497,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP117"/>
+  <dimension ref="A1:AP116"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="43.81640625" customWidth="true" bestFit="true"/>
@@ -5237,7 +5221,7 @@
         <v>223</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -5323,44 +5307,46 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="C24" t="s" s="2">
-        <v>226</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="M24" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O24" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="L24" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>82</v>
       </c>
@@ -5408,7 +5394,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>200</v>
+        <v>228</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -5432,7 +5418,7 @@
         <v>82</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>82</v>
+        <v>196</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>82</v>
@@ -5450,7 +5436,7 @@
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -5463,25 +5449,23 @@
         <v>82</v>
       </c>
       <c r="I25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J25" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="J25" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K25" t="s" s="2">
-        <v>114</v>
+        <v>230</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
@@ -5530,7 +5514,7 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -5542,22 +5526,22 @@
         <v>82</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>82</v>
+        <v>234</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>82</v>
+        <v>235</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>196</v>
+        <v>236</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>82</v>
+        <v>237</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>82</v>
@@ -5565,14 +5549,14 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>82</v>
+        <v>239</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -5591,17 +5575,17 @@
         <v>94</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -5650,7 +5634,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5665,19 +5649,19 @@
         <v>105</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>242</v>
+        <v>82</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>82</v>
@@ -5685,14 +5669,14 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -5711,18 +5695,18 @@
         <v>94</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="N27" s="2"/>
-      <c r="O27" t="s" s="2">
-        <v>248</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>82</v>
       </c>
@@ -5770,7 +5754,7 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5785,16 +5769,16 @@
         <v>105</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>82</v>
@@ -5803,46 +5787,48 @@
         <v>82</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>253</v>
+        <v>82</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J28" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>254</v>
+        <v>173</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="O28" s="2"/>
+        <v>259</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>82</v>
       </c>
@@ -5866,13 +5852,11 @@
         <v>82</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y28" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>261</v>
+      </c>
+      <c r="Y28" s="2"/>
       <c r="Z28" t="s" s="2">
-        <v>82</v>
+        <v>262</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>82</v>
@@ -5890,13 +5874,13 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>82</v>
@@ -5905,30 +5889,30 @@
         <v>105</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>82</v>
+        <v>264</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>82</v>
+        <v>267</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5939,31 +5923,31 @@
         <v>93</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>94</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>173</v>
+        <v>269</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>82</v>
@@ -5988,35 +5972,35 @@
         <v>82</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="Y29" s="2"/>
+        <v>177</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>274</v>
+      </c>
       <c r="Z29" t="s" s="2">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="AC29" s="2"/>
       <c r="AD29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>82</v>
@@ -6025,32 +6009,34 @@
         <v>105</v>
       </c>
       <c r="AK29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN29" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AO29" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AP29" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="B30" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="AL29" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="AO29" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="AP29" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="30" hidden="true">
-      <c r="A30" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="B30" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="C30" s="2"/>
+      <c r="C30" t="s" s="2">
+        <v>280</v>
+      </c>
       <c r="D30" t="s" s="2">
         <v>82</v>
       </c>
@@ -6059,7 +6045,7 @@
         <v>93</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>94</v>
@@ -6071,19 +6057,19 @@
         <v>82</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>82</v>
@@ -6111,26 +6097,28 @@
         <v>177</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="AC30" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -6154,37 +6142,35 @@
         <v>82</v>
       </c>
       <c r="AN30" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AO30" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AP30" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="31" hidden="true">
+      <c r="A31" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="B31" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AO30" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="AP30" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="B31" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="C31" t="s" s="2">
-        <v>285</v>
-      </c>
+      <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>82</v>
@@ -6193,20 +6179,16 @@
         <v>82</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>274</v>
+        <v>107</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>275</v>
+        <v>108</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>278</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>82</v>
       </c>
@@ -6230,13 +6212,13 @@
         <v>82</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>279</v>
+        <v>82</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>280</v>
+        <v>82</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>82</v>
@@ -6254,19 +6236,19 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>273</v>
+        <v>110</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>82</v>
@@ -6278,10 +6260,10 @@
         <v>82</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>282</v>
+        <v>111</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>283</v>
+        <v>82</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>82</v>
@@ -6289,21 +6271,21 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>82</v>
@@ -6315,15 +6297,17 @@
         <v>82</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>82</v>
@@ -6360,31 +6344,31 @@
         <v>82</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>82</v>
@@ -6405,46 +6389,48 @@
         <v>82</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>114</v>
+        <v>151</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>115</v>
+        <v>287</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>116</v>
+        <v>288</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O33" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>290</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
       </c>
@@ -6480,19 +6466,19 @@
         <v>82</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>121</v>
+        <v>291</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6504,7 +6490,7 @@
         <v>82</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>82</v>
@@ -6513,10 +6499,10 @@
         <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>82</v>
+        <v>292</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>111</v>
+        <v>293</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>82</v>
@@ -6525,12 +6511,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6538,35 +6524,31 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G34" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="G34" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="H34" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>151</v>
+        <v>107</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>292</v>
+        <v>108</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>295</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>82</v>
       </c>
@@ -6614,19 +6596,19 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>296</v>
+        <v>110</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>82</v>
@@ -6635,10 +6617,10 @@
         <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>297</v>
+        <v>82</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>298</v>
+        <v>111</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
@@ -6649,21 +6631,21 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>82</v>
@@ -6675,15 +6657,17 @@
         <v>82</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>82</v>
@@ -6720,31 +6704,31 @@
         <v>82</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>82</v>
@@ -6765,52 +6749,54 @@
         <v>82</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>115</v>
+        <v>300</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>116</v>
+        <v>301</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O36" s="2"/>
+        <v>302</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>303</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>82</v>
+        <v>304</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>82</v>
@@ -6840,31 +6826,31 @@
         <v>82</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>121</v>
+        <v>305</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>82</v>
@@ -6873,10 +6859,10 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>82</v>
+        <v>306</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>111</v>
+        <v>307</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -6885,12 +6871,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6898,13 +6884,13 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>82</v>
@@ -6913,26 +6899,24 @@
         <v>94</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>308</v>
-      </c>
+        <v>312</v>
+      </c>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>309</v>
+        <v>82</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>82</v>
@@ -6974,7 +6958,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6995,10 +6979,10 @@
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
@@ -7007,12 +6991,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7020,13 +7004,13 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>82</v>
@@ -7035,24 +7019,24 @@
         <v>94</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>107</v>
+        <v>173</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="O38" s="2"/>
+        <v>319</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" t="s" s="2">
+        <v>320</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q38" s="2"/>
       <c r="R38" t="s" s="2">
-        <v>82</v>
+        <v>321</v>
       </c>
       <c r="S38" t="s" s="2">
         <v>82</v>
@@ -7094,7 +7078,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -7115,10 +7099,10 @@
         <v>82</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
@@ -7127,12 +7111,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7140,13 +7124,13 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>82</v>
@@ -7155,24 +7139,24 @@
         <v>94</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>173</v>
+        <v>107</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q39" s="2"/>
       <c r="R39" t="s" s="2">
-        <v>326</v>
+        <v>82</v>
       </c>
       <c r="S39" t="s" s="2">
         <v>82</v>
@@ -7214,7 +7198,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -7235,10 +7219,10 @@
         <v>82</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -7249,10 +7233,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7275,17 +7259,19 @@
         <v>94</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>107</v>
+        <v>335</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>337</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>338</v>
+      </c>
       <c r="O40" t="s" s="2">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>82</v>
@@ -7334,7 +7320,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -7355,10 +7341,10 @@
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
@@ -7369,10 +7355,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7395,19 +7381,19 @@
         <v>94</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>340</v>
+        <v>107</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
@@ -7456,7 +7442,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -7477,10 +7463,10 @@
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -7489,26 +7475,26 @@
         <v>82</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>82</v>
+        <v>353</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>82</v>
@@ -7517,19 +7503,19 @@
         <v>94</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>107</v>
+        <v>269</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -7554,13 +7540,13 @@
         <v>82</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>82</v>
+        <v>358</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>82</v>
+        <v>359</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>82</v>
@@ -7578,10 +7564,10 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH42" t="s" s="2">
         <v>93</v>
@@ -7593,66 +7579,62 @@
         <v>105</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>82</v>
+        <v>360</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>82</v>
+        <v>361</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>82</v>
+        <v>364</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>82</v>
+        <v>365</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>358</v>
+        <v>82</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>274</v>
+        <v>107</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>359</v>
+        <v>108</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>362</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N43" s="2"/>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>82</v>
       </c>
@@ -7676,13 +7658,13 @@
         <v>82</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>363</v>
+        <v>82</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>364</v>
+        <v>82</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>82</v>
@@ -7700,10 +7682,10 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>357</v>
+        <v>110</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
         <v>93</v>
@@ -7712,44 +7694,44 @@
         <v>82</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>365</v>
+        <v>82</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>366</v>
+        <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>367</v>
+        <v>82</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>368</v>
+        <v>111</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>369</v>
+        <v>82</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>370</v>
+        <v>82</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>82</v>
@@ -7761,15 +7743,17 @@
         <v>82</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>82</v>
@@ -7806,31 +7790,31 @@
         <v>82</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>82</v>
@@ -7853,18 +7837,18 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>81</v>
@@ -7876,21 +7860,23 @@
         <v>82</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>114</v>
+        <v>151</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>115</v>
+        <v>287</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>116</v>
+        <v>288</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O45" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>290</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>82</v>
       </c>
@@ -7926,11 +7912,9 @@
         <v>82</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AC45" t="s" s="2">
-        <v>119</v>
-      </c>
+        <v>369</v>
+      </c>
+      <c r="AC45" s="2"/>
       <c r="AD45" t="s" s="2">
         <v>82</v>
       </c>
@@ -7938,7 +7922,7 @@
         <v>120</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>121</v>
+        <v>291</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7950,7 +7934,7 @@
         <v>82</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>82</v>
@@ -7959,10 +7943,10 @@
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>82</v>
+        <v>292</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>111</v>
+        <v>293</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
@@ -7973,12 +7957,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="C46" s="2"/>
+        <v>368</v>
+      </c>
+      <c r="C46" t="s" s="2">
+        <v>371</v>
+      </c>
       <c r="D46" t="s" s="2">
         <v>82</v>
       </c>
@@ -7987,7 +7973,7 @@
         <v>93</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>82</v>
@@ -8002,16 +7988,16 @@
         <v>151</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>82</v>
@@ -8048,17 +8034,19 @@
         <v>82</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="AC46" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -8079,10 +8067,10 @@
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
@@ -8093,20 +8081,18 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="B47" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="C47" t="s" s="2">
-        <v>376</v>
-      </c>
+      <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>93</v>
@@ -8118,23 +8104,19 @@
         <v>82</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>151</v>
+        <v>107</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>292</v>
+        <v>108</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>295</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>82</v>
       </c>
@@ -8182,19 +8164,19 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>296</v>
+        <v>110</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>82</v>
@@ -8203,10 +8185,10 @@
         <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>297</v>
+        <v>82</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>298</v>
+        <v>111</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
@@ -8217,21 +8199,21 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>82</v>
@@ -8243,15 +8225,17 @@
         <v>82</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -8288,31 +8272,31 @@
         <v>82</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>82</v>
@@ -8335,21 +8319,21 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>82</v>
@@ -8358,27 +8342,29 @@
         <v>82</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>115</v>
+        <v>300</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>116</v>
+        <v>301</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O49" s="2"/>
+        <v>302</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>303</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
-        <v>82</v>
+        <v>378</v>
       </c>
       <c r="S49" t="s" s="2">
         <v>82</v>
@@ -8408,31 +8394,31 @@
         <v>82</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>121</v>
+        <v>305</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>82</v>
@@ -8441,10 +8427,10 @@
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>82</v>
+        <v>306</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>111</v>
+        <v>307</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -8455,10 +8441,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8466,7 +8452,7 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>93</v>
@@ -8481,26 +8467,24 @@
         <v>94</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>308</v>
-      </c>
+        <v>312</v>
+      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q50" s="2"/>
       <c r="R50" t="s" s="2">
-        <v>383</v>
+        <v>82</v>
       </c>
       <c r="S50" t="s" s="2">
         <v>82</v>
@@ -8542,7 +8526,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8563,10 +8547,10 @@
         <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -8577,10 +8561,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8588,7 +8572,7 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>93</v>
@@ -8603,24 +8587,24 @@
         <v>94</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>107</v>
+        <v>173</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="O51" s="2"/>
+        <v>319</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" t="s" s="2">
+        <v>320</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q51" s="2"/>
       <c r="R51" t="s" s="2">
-        <v>82</v>
+        <v>383</v>
       </c>
       <c r="S51" t="s" s="2">
         <v>82</v>
@@ -8662,7 +8646,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8683,10 +8667,10 @@
         <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8697,10 +8681,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8708,7 +8692,7 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>93</v>
@@ -8723,24 +8707,24 @@
         <v>94</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>173</v>
+        <v>107</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q52" s="2"/>
       <c r="R52" t="s" s="2">
-        <v>388</v>
+        <v>82</v>
       </c>
       <c r="S52" t="s" s="2">
         <v>82</v>
@@ -8782,7 +8766,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8803,10 +8787,10 @@
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8817,10 +8801,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8843,17 +8827,19 @@
         <v>94</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>107</v>
+        <v>335</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>337</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>338</v>
+      </c>
       <c r="O53" t="s" s="2">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>82</v>
@@ -8902,7 +8888,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8923,10 +8909,10 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
@@ -8937,10 +8923,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8963,19 +8949,19 @@
         <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>340</v>
+        <v>107</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -9024,7 +9010,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -9045,10 +9031,10 @@
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -9057,12 +9043,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9070,13 +9056,13 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>82</v>
@@ -9085,19 +9071,19 @@
         <v>94</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>107</v>
+        <v>390</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>350</v>
+        <v>391</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>351</v>
+        <v>392</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>352</v>
+        <v>393</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>353</v>
+        <v>394</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -9146,7 +9132,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>354</v>
+        <v>389</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -9161,30 +9147,30 @@
         <v>105</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>82</v>
+        <v>395</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>355</v>
+        <v>396</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>356</v>
+        <v>397</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>82</v>
+        <v>398</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9192,13 +9178,13 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>82</v>
@@ -9207,20 +9193,18 @@
         <v>94</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>399</v>
-      </c>
+        <v>403</v>
+      </c>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>82</v>
       </c>
@@ -9268,13 +9252,13 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>82</v>
@@ -9283,19 +9267,19 @@
         <v>105</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>400</v>
+        <v>82</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>401</v>
+        <v>362</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>82</v>
@@ -9303,21 +9287,21 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>82</v>
+        <v>406</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>82</v>
@@ -9329,18 +9313,20 @@
         <v>94</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="O57" s="2"/>
+        <v>410</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>411</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>82</v>
       </c>
@@ -9388,13 +9374,13 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>82</v>
@@ -9403,44 +9389,44 @@
         <v>105</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>82</v>
+        <v>412</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>367</v>
+        <v>413</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>403</v>
+        <v>415</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G58" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>82</v>
@@ -9449,19 +9435,19 @@
         <v>94</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -9510,7 +9496,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9519,50 +9505,50 @@
         <v>93</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>82</v>
+        <v>423</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>105</v>
+        <v>424</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>422</v>
+        <v>82</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>82</v>
@@ -9571,20 +9557,18 @@
         <v>94</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>423</v>
+        <v>129</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>427</v>
-      </c>
+        <v>432</v>
+      </c>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>82</v>
       </c>
@@ -9632,7 +9616,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9641,25 +9625,25 @@
         <v>93</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>428</v>
+        <v>82</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>429</v>
+        <v>105</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>430</v>
+        <v>82</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>82</v>
@@ -9667,10 +9651,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9681,7 +9665,7 @@
         <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>82</v>
@@ -9693,18 +9677,18 @@
         <v>94</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>129</v>
+        <v>437</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="O60" s="2"/>
+        <v>439</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" t="s" s="2">
+        <v>440</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
       </c>
@@ -9752,13 +9736,13 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>82</v>
@@ -9767,19 +9751,19 @@
         <v>105</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>82</v>
+        <v>441</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>82</v>
@@ -9787,10 +9771,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9801,10 +9785,10 @@
         <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>82</v>
@@ -9813,17 +9797,19 @@
         <v>94</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>447</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>448</v>
+      </c>
       <c r="O61" t="s" s="2">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -9860,59 +9846,59 @@
         <v>82</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>450</v>
+      </c>
+      <c r="AC61" s="2"/>
       <c r="AD61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>82</v>
+        <v>451</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>82</v>
+        <v>452</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>446</v>
+        <v>82</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>82</v>
+        <v>453</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>449</v>
+        <v>82</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>82</v>
+        <v>456</v>
       </c>
     </row>
-    <row r="62" hidden="true">
+    <row r="62">
       <c r="A62" t="s" s="2">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="C62" s="2"/>
+        <v>445</v>
+      </c>
+      <c r="C62" t="s" s="2">
+        <v>458</v>
+      </c>
       <c r="D62" t="s" s="2">
         <v>82</v>
       </c>
@@ -9933,19 +9919,19 @@
         <v>94</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>82</v>
@@ -9982,17 +9968,19 @@
         <v>82</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="AC62" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>456</v>
+        <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -10001,7 +9989,7 @@
         <v>93</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>105</v>
@@ -10010,31 +9998,29 @@
         <v>82</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="AM62" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="AO62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP62" t="s" s="2">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="63" hidden="true">
+      <c r="A63" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="AN62" t="s" s="2">
+      <c r="B63" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="AO62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP62" t="s" s="2">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="C63" t="s" s="2">
-        <v>463</v>
-      </c>
+      <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
         <v>82</v>
       </c>
@@ -10046,29 +10032,25 @@
         <v>93</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>451</v>
+        <v>107</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>452</v>
+        <v>108</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>454</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>82</v>
       </c>
@@ -10116,7 +10098,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>450</v>
+        <v>110</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -10125,47 +10107,47 @@
         <v>93</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>457</v>
+        <v>82</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>458</v>
+        <v>82</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>459</v>
+        <v>82</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>460</v>
+        <v>111</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>461</v>
+        <v>82</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>82</v>
@@ -10177,15 +10159,17 @@
         <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N64" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>82</v>
@@ -10222,31 +10206,31 @@
         <v>82</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>82</v>
@@ -10267,46 +10251,48 @@
         <v>82</v>
       </c>
     </row>
-    <row r="65" hidden="true">
+    <row r="65">
       <c r="A65" t="s" s="2">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>114</v>
+        <v>465</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>115</v>
+        <v>466</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>116</v>
+        <v>467</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O65" s="2"/>
+        <v>468</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>469</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>82</v>
       </c>
@@ -10342,31 +10328,31 @@
         <v>82</v>
       </c>
       <c r="AB65" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC65" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>121</v>
+        <v>470</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>82</v>
@@ -10375,10 +10361,10 @@
         <v>82</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>82</v>
+        <v>471</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>111</v>
+        <v>472</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
@@ -10387,12 +10373,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10400,39 +10386,39 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G66" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I66" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="I66" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="J66" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>470</v>
+        <v>173</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>473</v>
-      </c>
+        <v>476</v>
+      </c>
+      <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q66" s="2"/>
+      <c r="Q66" t="s" s="2">
+        <v>478</v>
+      </c>
       <c r="R66" t="s" s="2">
         <v>82</v>
       </c>
@@ -10452,13 +10438,13 @@
         <v>82</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>82</v>
+        <v>261</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>82</v>
+        <v>479</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>82</v>
+        <v>480</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>82</v>
@@ -10476,7 +10462,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10497,10 +10483,10 @@
         <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>82</v>
@@ -10509,12 +10495,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="67" hidden="true">
+    <row r="67">
       <c r="A67" t="s" s="2">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10522,39 +10508,37 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G67" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I67" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J67" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>173</v>
+        <v>107</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q67" t="s" s="2">
-        <v>483</v>
-      </c>
+      <c r="Q67" s="2"/>
       <c r="R67" t="s" s="2">
         <v>82</v>
       </c>
@@ -10574,13 +10558,13 @@
         <v>82</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>266</v>
+        <v>82</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>484</v>
+        <v>82</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>485</v>
+        <v>82</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>82</v>
@@ -10598,7 +10582,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10619,10 +10603,10 @@
         <v>82</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>82</v>
@@ -10633,10 +10617,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10659,24 +10643,24 @@
         <v>94</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q68" s="2"/>
       <c r="R68" t="s" s="2">
-        <v>82</v>
+        <v>497</v>
       </c>
       <c r="S68" t="s" s="2">
         <v>82</v>
@@ -10718,7 +10702,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10727,7 +10711,7 @@
         <v>93</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>82</v>
+        <v>499</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>105</v>
@@ -10739,10 +10723,10 @@
         <v>82</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
@@ -10753,10 +10737,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10779,24 +10763,26 @@
         <v>94</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="N69" s="2"/>
+        <v>503</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>504</v>
+      </c>
       <c r="O69" t="s" s="2">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q69" s="2"/>
       <c r="R69" t="s" s="2">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="S69" t="s" s="2">
         <v>82</v>
@@ -10838,7 +10824,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10847,7 +10833,7 @@
         <v>93</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>504</v>
+        <v>82</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>105</v>
@@ -10859,10 +10845,10 @@
         <v>82</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
@@ -10873,10 +10859,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10884,7 +10870,7 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G70" t="s" s="2">
         <v>93</v>
@@ -10896,29 +10882,29 @@
         <v>82</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>173</v>
+        <v>269</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q70" s="2"/>
       <c r="R70" t="s" s="2">
-        <v>511</v>
+        <v>82</v>
       </c>
       <c r="S70" t="s" s="2">
         <v>82</v>
@@ -10936,13 +10922,13 @@
         <v>82</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>82</v>
+        <v>514</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>82</v>
+        <v>515</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>82</v>
@@ -10960,7 +10946,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10969,7 +10955,7 @@
         <v>93</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>82</v>
+        <v>516</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>105</v>
@@ -10981,10 +10967,10 @@
         <v>82</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>495</v>
+        <v>196</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>82</v>
@@ -10993,12 +10979,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11012,7 +10998,7 @@
         <v>93</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>82</v>
@@ -11021,20 +11007,16 @@
         <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>274</v>
+        <v>107</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>515</v>
+        <v>108</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>518</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>82</v>
       </c>
@@ -11058,13 +11040,13 @@
         <v>82</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>519</v>
+        <v>82</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>520</v>
+        <v>82</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>82</v>
@@ -11082,7 +11064,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>514</v>
+        <v>110</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -11091,10 +11073,10 @@
         <v>93</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>521</v>
+        <v>82</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>82</v>
@@ -11103,10 +11085,10 @@
         <v>82</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>196</v>
+        <v>82</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>522</v>
+        <v>111</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
@@ -11117,21 +11099,21 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>82</v>
@@ -11143,15 +11125,17 @@
         <v>82</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N72" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>82</v>
@@ -11188,31 +11172,31 @@
         <v>82</v>
       </c>
       <c r="AB72" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC72" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE72" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>82</v>
@@ -11235,14 +11219,14 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -11258,21 +11242,23 @@
         <v>82</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>114</v>
+        <v>151</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>115</v>
+        <v>287</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>116</v>
+        <v>288</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O73" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>290</v>
+      </c>
       <c r="P73" t="s" s="2">
         <v>82</v>
       </c>
@@ -11308,19 +11294,19 @@
         <v>82</v>
       </c>
       <c r="AB73" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC73" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>121</v>
+        <v>291</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11332,7 +11318,7 @@
         <v>82</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>82</v>
@@ -11341,10 +11327,10 @@
         <v>82</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>82</v>
+        <v>292</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>111</v>
+        <v>293</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>82</v>
@@ -11355,10 +11341,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11369,7 +11355,7 @@
         <v>80</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>82</v>
@@ -11378,23 +11364,19 @@
         <v>82</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>151</v>
+        <v>107</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>292</v>
+        <v>108</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>295</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N74" s="2"/>
+      <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>82</v>
       </c>
@@ -11442,19 +11424,19 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>296</v>
+        <v>110</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>82</v>
@@ -11463,10 +11445,10 @@
         <v>82</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>297</v>
+        <v>82</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>298</v>
+        <v>111</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
@@ -11477,21 +11459,21 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>82</v>
@@ -11503,15 +11485,17 @@
         <v>82</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N75" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>82</v>
@@ -11548,31 +11532,31 @@
         <v>82</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC75" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>82</v>
@@ -11595,21 +11579,21 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>82</v>
@@ -11618,21 +11602,23 @@
         <v>82</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>115</v>
+        <v>300</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>116</v>
+        <v>301</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O76" s="2"/>
+        <v>302</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>303</v>
+      </c>
       <c r="P76" t="s" s="2">
         <v>82</v>
       </c>
@@ -11668,31 +11654,31 @@
         <v>82</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC76" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>121</v>
+        <v>305</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>82</v>
@@ -11701,10 +11687,10 @@
         <v>82</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>82</v>
+        <v>306</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>111</v>
+        <v>307</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>82</v>
@@ -11715,10 +11701,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11726,7 +11712,7 @@
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G77" t="s" s="2">
         <v>93</v>
@@ -11741,20 +11727,18 @@
         <v>94</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>308</v>
-      </c>
+        <v>312</v>
+      </c>
+      <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>82</v>
       </c>
@@ -11802,7 +11786,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11823,10 +11807,10 @@
         <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>82</v>
@@ -11837,10 +11821,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11848,7 +11832,7 @@
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G78" t="s" s="2">
         <v>93</v>
@@ -11863,18 +11847,18 @@
         <v>94</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>107</v>
+        <v>173</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="O78" s="2"/>
+        <v>319</v>
+      </c>
+      <c r="N78" s="2"/>
+      <c r="O78" t="s" s="2">
+        <v>320</v>
+      </c>
       <c r="P78" t="s" s="2">
         <v>82</v>
       </c>
@@ -11922,7 +11906,7 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11943,10 +11927,10 @@
         <v>82</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>82</v>
@@ -11957,10 +11941,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11968,7 +11952,7 @@
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G79" t="s" s="2">
         <v>93</v>
@@ -11983,17 +11967,17 @@
         <v>94</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>173</v>
+        <v>107</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>82</v>
@@ -12042,7 +12026,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -12063,10 +12047,10 @@
         <v>82</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>82</v>
@@ -12077,10 +12061,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12103,17 +12087,19 @@
         <v>94</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>107</v>
+        <v>335</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="N80" s="2"/>
+        <v>337</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>338</v>
+      </c>
       <c r="O80" t="s" s="2">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>82</v>
@@ -12162,7 +12148,7 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -12183,10 +12169,10 @@
         <v>82</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>82</v>
@@ -12197,10 +12183,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12223,19 +12209,19 @@
         <v>94</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>340</v>
+        <v>107</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>82</v>
@@ -12284,7 +12270,7 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -12305,10 +12291,10 @@
         <v>82</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>82</v>
@@ -12319,21 +12305,21 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>82</v>
+        <v>530</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>82</v>
@@ -12342,22 +12328,22 @@
         <v>82</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>107</v>
+        <v>269</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>350</v>
+        <v>531</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>351</v>
+        <v>532</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>352</v>
+        <v>533</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>353</v>
+        <v>534</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>82</v>
@@ -12382,13 +12368,11 @@
         <v>82</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y82" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="Y82" s="2"/>
       <c r="Z82" t="s" s="2">
-        <v>82</v>
+        <v>535</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>82</v>
@@ -12406,13 +12390,13 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>354</v>
+        <v>529</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>82</v>
@@ -12424,31 +12408,31 @@
         <v>82</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>82</v>
+        <v>536</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>355</v>
+        <v>537</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>356</v>
+        <v>538</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>82</v>
+        <v>539</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>535</v>
+        <v>82</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -12467,19 +12451,19 @@
         <v>82</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>274</v>
+        <v>541</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>82</v>
@@ -12504,29 +12488,31 @@
         <v>82</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="Y83" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF83" t="s" s="2">
         <v>540</v>
-      </c>
-      <c r="AA83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF83" t="s" s="2">
-        <v>534</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12544,27 +12530,27 @@
         <v>82</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>541</v>
+        <v>82</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>544</v>
+        <v>82</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12575,7 +12561,7 @@
         <v>80</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>82</v>
@@ -12587,20 +12573,18 @@
         <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>546</v>
+        <v>269</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>550</v>
-      </c>
+        <v>551</v>
+      </c>
+      <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>82</v>
       </c>
@@ -12624,13 +12608,11 @@
         <v>82</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y84" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="Y84" s="2"/>
       <c r="Z84" t="s" s="2">
-        <v>82</v>
+        <v>552</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>82</v>
@@ -12648,13 +12630,13 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>82</v>
@@ -12666,27 +12648,27 @@
         <v>82</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>82</v>
+        <v>553</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>82</v>
+        <v>556</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12709,17 +12691,15 @@
         <v>82</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>274</v>
+        <v>107</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>554</v>
+        <v>108</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>556</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N85" s="2"/>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>82</v>
@@ -12744,11 +12724,13 @@
         <v>82</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="Y85" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z85" t="s" s="2">
-        <v>557</v>
+        <v>82</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>82</v>
@@ -12766,7 +12748,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>553</v>
+        <v>110</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12778,44 +12760,44 @@
         <v>82</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>558</v>
+        <v>82</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>559</v>
+        <v>82</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>560</v>
+        <v>111</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>561</v>
+        <v>82</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>82</v>
@@ -12827,15 +12809,17 @@
         <v>82</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N86" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>82</v>
@@ -12872,31 +12856,31 @@
         <v>82</v>
       </c>
       <c r="AB86" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC86" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>82</v>
@@ -12919,14 +12903,14 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -12942,21 +12926,23 @@
         <v>82</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>114</v>
+        <v>151</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>115</v>
+        <v>287</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>116</v>
+        <v>288</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O87" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="O87" t="s" s="2">
+        <v>290</v>
+      </c>
       <c r="P87" t="s" s="2">
         <v>82</v>
       </c>
@@ -12980,31 +12966,29 @@
         <v>82</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y87" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="Y87" s="2"/>
       <c r="Z87" t="s" s="2">
-        <v>82</v>
+        <v>560</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC87" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>121</v>
+        <v>291</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -13016,7 +13000,7 @@
         <v>82</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>82</v>
@@ -13025,10 +13009,10 @@
         <v>82</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>82</v>
+        <v>292</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>111</v>
+        <v>293</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>82</v>
@@ -13039,10 +13023,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13053,7 +13037,7 @@
         <v>80</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>82</v>
@@ -13065,19 +13049,19 @@
         <v>94</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>151</v>
+        <v>107</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>292</v>
+        <v>345</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>293</v>
+        <v>346</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>294</v>
+        <v>347</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>295</v>
+        <v>348</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>82</v>
@@ -13102,11 +13086,13 @@
         <v>82</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="Y88" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y88" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z88" t="s" s="2">
-        <v>565</v>
+        <v>82</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>82</v>
@@ -13124,13 +13110,13 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>296</v>
+        <v>349</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>82</v>
@@ -13145,10 +13131,10 @@
         <v>82</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>297</v>
+        <v>350</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>298</v>
+        <v>351</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>82</v>
@@ -13157,12 +13143,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="89" hidden="true">
+    <row r="89">
       <c r="A89" t="s" s="2">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13176,28 +13162,28 @@
         <v>93</v>
       </c>
       <c r="H89" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>107</v>
+        <v>269</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>350</v>
+        <v>563</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>351</v>
+        <v>564</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>352</v>
+        <v>565</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>353</v>
+        <v>566</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>82</v>
@@ -13222,13 +13208,11 @@
         <v>82</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y89" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="Y89" s="2"/>
       <c r="Z89" t="s" s="2">
-        <v>82</v>
+        <v>567</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>82</v>
@@ -13246,7 +13230,7 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>354</v>
+        <v>562</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -13267,10 +13251,10 @@
         <v>82</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>355</v>
+        <v>568</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>356</v>
+        <v>569</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>82</v>
@@ -13279,12 +13263,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13298,7 +13282,7 @@
         <v>93</v>
       </c>
       <c r="H90" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I90" t="s" s="2">
         <v>82</v>
@@ -13307,20 +13291,16 @@
         <v>82</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>274</v>
+        <v>107</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>568</v>
+        <v>108</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>571</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N90" s="2"/>
+      <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>82</v>
       </c>
@@ -13344,11 +13324,13 @@
         <v>82</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="Y90" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z90" t="s" s="2">
-        <v>572</v>
+        <v>82</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>82</v>
@@ -13366,7 +13348,7 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>567</v>
+        <v>110</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -13378,7 +13360,7 @@
         <v>82</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>82</v>
@@ -13387,10 +13369,10 @@
         <v>82</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>573</v>
+        <v>82</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>574</v>
+        <v>111</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>82</v>
@@ -13401,21 +13383,21 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>82</v>
@@ -13427,15 +13409,17 @@
         <v>82</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N91" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N91" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>82</v>
@@ -13472,31 +13456,31 @@
         <v>82</v>
       </c>
       <c r="AB91" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC91" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE91" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>82</v>
@@ -13519,14 +13503,14 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
@@ -13542,21 +13526,23 @@
         <v>82</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>114</v>
+        <v>151</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>115</v>
+        <v>287</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>116</v>
+        <v>288</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O92" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="O92" t="s" s="2">
+        <v>290</v>
+      </c>
       <c r="P92" t="s" s="2">
         <v>82</v>
       </c>
@@ -13580,31 +13566,29 @@
         <v>82</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y92" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="Y92" s="2"/>
       <c r="Z92" t="s" s="2">
-        <v>82</v>
+        <v>573</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB92" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC92" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE92" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>121</v>
+        <v>291</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13616,7 +13600,7 @@
         <v>82</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>82</v>
@@ -13625,10 +13609,10 @@
         <v>82</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>82</v>
+        <v>292</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>111</v>
+        <v>293</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>82</v>
@@ -13639,10 +13623,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13653,7 +13637,7 @@
         <v>80</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>82</v>
@@ -13665,19 +13649,19 @@
         <v>94</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>151</v>
+        <v>107</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>292</v>
+        <v>345</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>293</v>
+        <v>346</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>294</v>
+        <v>347</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>295</v>
+        <v>348</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>82</v>
@@ -13702,11 +13686,13 @@
         <v>82</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="Y93" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y93" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z93" t="s" s="2">
-        <v>578</v>
+        <v>82</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>82</v>
@@ -13724,13 +13710,13 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>296</v>
+        <v>349</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>82</v>
@@ -13745,10 +13731,10 @@
         <v>82</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>297</v>
+        <v>350</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>298</v>
+        <v>351</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>82</v>
@@ -13759,10 +13745,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13782,23 +13768,21 @@
         <v>82</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>107</v>
+        <v>576</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>350</v>
+        <v>577</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>351</v>
+        <v>578</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="O94" t="s" s="2">
-        <v>353</v>
-      </c>
+        <v>579</v>
+      </c>
+      <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>82</v>
       </c>
@@ -13846,7 +13830,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>354</v>
+        <v>575</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13864,27 +13848,27 @@
         <v>82</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>82</v>
+        <v>580</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>355</v>
+        <v>581</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>356</v>
+        <v>582</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>82</v>
+        <v>583</v>
       </c>
     </row>
-    <row r="95" hidden="true">
+    <row r="95">
       <c r="A95" t="s" s="2">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13898,7 +13882,7 @@
         <v>93</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I95" t="s" s="2">
         <v>82</v>
@@ -13907,16 +13891,16 @@
         <v>82</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -13966,7 +13950,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -13984,27 +13968,27 @@
         <v>82</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>588</v>
+        <v>592</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14015,10 +13999,10 @@
         <v>80</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H96" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I96" t="s" s="2">
         <v>82</v>
@@ -14027,18 +14011,20 @@
         <v>82</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="O96" s="2"/>
+        <v>597</v>
+      </c>
+      <c r="O96" t="s" s="2">
+        <v>598</v>
+      </c>
       <c r="P96" t="s" s="2">
         <v>82</v>
       </c>
@@ -14086,45 +14072,45 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>105</v>
+        <v>599</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>594</v>
+        <v>82</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP96" t="s" s="2">
-        <v>597</v>
+        <v>82</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14135,7 +14121,7 @@
         <v>80</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>82</v>
@@ -14147,20 +14133,16 @@
         <v>82</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>599</v>
+        <v>107</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>600</v>
+        <v>108</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>603</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N97" s="2"/>
+      <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>82</v>
       </c>
@@ -14208,19 +14190,19 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>598</v>
+        <v>110</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>604</v>
+        <v>82</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>82</v>
@@ -14229,10 +14211,10 @@
         <v>82</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>605</v>
+        <v>82</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>606</v>
+        <v>111</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>82</v>
@@ -14243,21 +14225,21 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>82</v>
@@ -14269,15 +14251,17 @@
         <v>82</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N98" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>82</v>
@@ -14326,19 +14310,19 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>82</v>
@@ -14361,14 +14345,14 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>113</v>
+        <v>605</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -14381,24 +14365,26 @@
         <v>82</v>
       </c>
       <c r="I99" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K99" t="s" s="2">
         <v>114</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>115</v>
+        <v>606</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>116</v>
+        <v>607</v>
       </c>
       <c r="N99" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="O99" s="2"/>
+      <c r="O99" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="P99" t="s" s="2">
         <v>82</v>
       </c>
@@ -14446,7 +14432,7 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>121</v>
+        <v>608</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -14470,7 +14456,7 @@
         <v>82</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>111</v>
+        <v>196</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>82</v>
@@ -14488,26 +14474,26 @@
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>610</v>
+        <v>82</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I100" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>114</v>
+        <v>610</v>
       </c>
       <c r="L100" t="s" s="2">
         <v>611</v>
@@ -14515,12 +14501,8 @@
       <c r="M100" t="s" s="2">
         <v>612</v>
       </c>
-      <c r="N100" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>232</v>
-      </c>
+      <c r="N100" s="2"/>
+      <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>82</v>
       </c>
@@ -14568,19 +14550,19 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="AG100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH100" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI100" t="s" s="2">
         <v>613</v>
       </c>
-      <c r="AG100" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH100" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI100" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AJ100" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>82</v>
@@ -14589,10 +14571,10 @@
         <v>82</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>82</v>
+        <v>614</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>196</v>
+        <v>615</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>82</v>
@@ -14603,10 +14585,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14629,13 +14611,13 @@
         <v>82</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>615</v>
+        <v>610</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -14686,7 +14668,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14695,7 +14677,7 @@
         <v>93</v>
       </c>
       <c r="AI101" t="s" s="2">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="AJ101" t="s" s="2">
         <v>105</v>
@@ -14707,10 +14689,10 @@
         <v>82</v>
       </c>
       <c r="AM101" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="AN101" t="s" s="2">
         <v>619</v>
-      </c>
-      <c r="AN101" t="s" s="2">
-        <v>620</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>82</v>
@@ -14721,10 +14703,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14747,16 +14729,20 @@
         <v>82</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>615</v>
+        <v>269</v>
       </c>
       <c r="L102" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="M102" t="s" s="2">
         <v>622</v>
       </c>
-      <c r="M102" t="s" s="2">
+      <c r="N102" t="s" s="2">
         <v>623</v>
       </c>
-      <c r="N102" s="2"/>
-      <c r="O102" s="2"/>
+      <c r="O102" t="s" s="2">
+        <v>624</v>
+      </c>
       <c r="P102" t="s" s="2">
         <v>82</v>
       </c>
@@ -14780,13 +14766,13 @@
         <v>82</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>82</v>
+        <v>625</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>82</v>
+        <v>626</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>82</v>
@@ -14804,7 +14790,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14813,7 +14799,7 @@
         <v>93</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>618</v>
+        <v>82</v>
       </c>
       <c r="AJ102" t="s" s="2">
         <v>105</v>
@@ -14822,13 +14808,13 @@
         <v>82</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>82</v>
+        <v>627</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>619</v>
+        <v>628</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>624</v>
+        <v>538</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>82</v>
@@ -14839,10 +14825,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14853,7 +14839,7 @@
         <v>80</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>82</v>
@@ -14865,19 +14851,19 @@
         <v>82</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>82</v>
@@ -14902,13 +14888,13 @@
         <v>82</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>82</v>
@@ -14926,13 +14912,13 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI103" t="s" s="2">
         <v>82</v>
@@ -14944,13 +14930,13 @@
         <v>82</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>632</v>
+        <v>627</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>82</v>
@@ -14961,10 +14947,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14975,7 +14961,7 @@
         <v>80</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H104" t="s" s="2">
         <v>82</v>
@@ -14987,19 +14973,17 @@
         <v>82</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>274</v>
+        <v>637</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>637</v>
-      </c>
+        <v>639</v>
+      </c>
+      <c r="N104" s="2"/>
       <c r="O104" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>82</v>
@@ -15024,13 +15008,13 @@
         <v>82</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>163</v>
+        <v>82</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>639</v>
+        <v>82</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>640</v>
+        <v>82</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>82</v>
@@ -15048,13 +15032,13 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI104" t="s" s="2">
         <v>82</v>
@@ -15066,13 +15050,13 @@
         <v>82</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>632</v>
+        <v>82</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>633</v>
+        <v>82</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>543</v>
+        <v>641</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>82</v>
@@ -15083,10 +15067,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15109,7 +15093,7 @@
         <v>82</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>642</v>
+        <v>107</v>
       </c>
       <c r="L105" t="s" s="2">
         <v>643</v>
@@ -15118,9 +15102,7 @@
         <v>644</v>
       </c>
       <c r="N105" s="2"/>
-      <c r="O105" t="s" s="2">
-        <v>645</v>
-      </c>
+      <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
         <v>82</v>
       </c>
@@ -15168,7 +15150,7 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -15189,10 +15171,10 @@
         <v>82</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>82</v>
+        <v>614</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>82</v>
@@ -15203,10 +15185,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15217,7 +15199,7 @@
         <v>80</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>82</v>
@@ -15226,10 +15208,10 @@
         <v>82</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>107</v>
+        <v>647</v>
       </c>
       <c r="L106" t="s" s="2">
         <v>648</v>
@@ -15237,7 +15219,9 @@
       <c r="M106" t="s" s="2">
         <v>649</v>
       </c>
-      <c r="N106" s="2"/>
+      <c r="N106" t="s" s="2">
+        <v>650</v>
+      </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
         <v>82</v>
@@ -15286,13 +15270,13 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>82</v>
@@ -15307,10 +15291,10 @@
         <v>82</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>619</v>
+        <v>651</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>82</v>
@@ -15321,10 +15305,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15347,16 +15331,16 @@
         <v>94</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -15406,7 +15390,7 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15427,10 +15411,10 @@
         <v>82</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>656</v>
+        <v>651</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>82</v>
@@ -15439,12 +15423,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="108" hidden="true">
+    <row r="108">
       <c r="A108" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15458,7 +15442,7 @@
         <v>81</v>
       </c>
       <c r="H108" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I108" t="s" s="2">
         <v>82</v>
@@ -15467,18 +15451,20 @@
         <v>94</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>659</v>
+        <v>594</v>
       </c>
       <c r="L108" t="s" s="2">
         <v>660</v>
       </c>
       <c r="M108" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="N108" t="s" s="2">
         <v>661</v>
       </c>
-      <c r="N108" t="s" s="2">
+      <c r="O108" t="s" s="2">
         <v>662</v>
       </c>
-      <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
         <v>82</v>
       </c>
@@ -15526,7 +15512,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15538,7 +15524,7 @@
         <v>82</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>105</v>
+        <v>663</v>
       </c>
       <c r="AK108" t="s" s="2">
         <v>82</v>
@@ -15547,10 +15533,10 @@
         <v>82</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>656</v>
+        <v>664</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>82</v>
@@ -15559,12 +15545,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15575,32 +15561,28 @@
         <v>80</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H109" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I109" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>599</v>
+        <v>107</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>665</v>
+        <v>108</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>665</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>666</v>
-      </c>
-      <c r="O109" t="s" s="2">
-        <v>667</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N109" s="2"/>
+      <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>82</v>
       </c>
@@ -15648,19 +15630,19 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>664</v>
+        <v>110</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI109" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>668</v>
+        <v>82</v>
       </c>
       <c r="AK109" t="s" s="2">
         <v>82</v>
@@ -15669,10 +15651,10 @@
         <v>82</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>669</v>
+        <v>82</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>670</v>
+        <v>111</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>82</v>
@@ -15683,21 +15665,21 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H110" t="s" s="2">
         <v>82</v>
@@ -15709,15 +15691,17 @@
         <v>82</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N110" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N110" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
         <v>82</v>
@@ -15766,19 +15750,19 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI110" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK110" t="s" s="2">
         <v>82</v>
@@ -15801,14 +15785,14 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>113</v>
+        <v>605</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
@@ -15821,24 +15805,26 @@
         <v>82</v>
       </c>
       <c r="I111" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K111" t="s" s="2">
         <v>114</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>115</v>
+        <v>606</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>116</v>
+        <v>607</v>
       </c>
       <c r="N111" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="O111" s="2"/>
+      <c r="O111" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="P111" t="s" s="2">
         <v>82</v>
       </c>
@@ -15886,7 +15872,7 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>121</v>
+        <v>608</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -15910,7 +15896,7 @@
         <v>82</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>111</v>
+        <v>196</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>82</v>
@@ -15919,47 +15905,47 @@
         <v>82</v>
       </c>
     </row>
-    <row r="112" hidden="true">
+    <row r="112">
       <c r="A112" t="s" s="2">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>610</v>
+        <v>82</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H112" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I112" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J112" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>114</v>
+        <v>269</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>611</v>
+        <v>670</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>612</v>
+        <v>671</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>117</v>
+        <v>672</v>
       </c>
       <c r="O112" t="s" s="2">
-        <v>232</v>
+        <v>673</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>82</v>
@@ -15984,13 +15970,13 @@
         <v>82</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>82</v>
+        <v>358</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>82</v>
+        <v>359</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>82</v>
@@ -16008,34 +15994,34 @@
         <v>82</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>613</v>
+        <v>669</v>
       </c>
       <c r="AG112" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI112" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK112" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>82</v>
+        <v>674</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>82</v>
+        <v>362</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>196</v>
+        <v>363</v>
       </c>
       <c r="AO112" t="s" s="2">
-        <v>82</v>
+        <v>364</v>
       </c>
       <c r="AP112" t="s" s="2">
         <v>82</v>
@@ -16043,10 +16029,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16054,7 +16040,7 @@
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G113" t="s" s="2">
         <v>93</v>
@@ -16069,19 +16055,19 @@
         <v>94</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>274</v>
+        <v>676</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>678</v>
+        <v>449</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>82</v>
@@ -16109,10 +16095,10 @@
         <v>155</v>
       </c>
       <c r="Y113" t="s" s="2">
-        <v>363</v>
+        <v>680</v>
       </c>
       <c r="Z113" t="s" s="2">
-        <v>364</v>
+        <v>681</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>82</v>
@@ -16130,16 +16116,16 @@
         <v>82</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="AG113" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH113" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AI113" t="s" s="2">
-        <v>82</v>
+        <v>682</v>
       </c>
       <c r="AJ113" t="s" s="2">
         <v>105</v>
@@ -16148,27 +16134,27 @@
         <v>82</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>367</v>
+        <v>454</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>368</v>
+        <v>455</v>
       </c>
       <c r="AO113" t="s" s="2">
-        <v>369</v>
+        <v>82</v>
       </c>
       <c r="AP113" t="s" s="2">
-        <v>82</v>
+        <v>456</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16188,22 +16174,22 @@
         <v>82</v>
       </c>
       <c r="J114" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>681</v>
+        <v>269</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>454</v>
+        <v>513</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>82</v>
@@ -16231,10 +16217,10 @@
         <v>155</v>
       </c>
       <c r="Y114" t="s" s="2">
-        <v>685</v>
+        <v>514</v>
       </c>
       <c r="Z114" t="s" s="2">
-        <v>686</v>
+        <v>515</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>82</v>
@@ -16252,7 +16238,7 @@
         <v>82</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -16261,7 +16247,7 @@
         <v>93</v>
       </c>
       <c r="AI114" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="AJ114" t="s" s="2">
         <v>105</v>
@@ -16270,22 +16256,22 @@
         <v>82</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>688</v>
+        <v>82</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>459</v>
+        <v>196</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>460</v>
+        <v>517</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP114" t="s" s="2">
-        <v>461</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
         <v>689</v>
       </c>
@@ -16294,17 +16280,17 @@
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
-        <v>82</v>
+        <v>530</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H115" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I115" t="s" s="2">
         <v>82</v>
@@ -16313,19 +16299,19 @@
         <v>82</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>690</v>
+        <v>531</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>691</v>
+        <v>532</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>692</v>
+        <v>533</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>518</v>
+        <v>534</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>82</v>
@@ -16353,10 +16339,10 @@
         <v>155</v>
       </c>
       <c r="Y115" t="s" s="2">
-        <v>519</v>
+        <v>690</v>
       </c>
       <c r="Z115" t="s" s="2">
-        <v>520</v>
+        <v>535</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>82</v>
@@ -16380,10 +16366,10 @@
         <v>80</v>
       </c>
       <c r="AH115" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI115" t="s" s="2">
-        <v>693</v>
+        <v>82</v>
       </c>
       <c r="AJ115" t="s" s="2">
         <v>105</v>
@@ -16392,31 +16378,31 @@
         <v>82</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>82</v>
+        <v>536</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>196</v>
+        <v>537</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>522</v>
+        <v>538</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP115" t="s" s="2">
-        <v>82</v>
+        <v>539</v>
       </c>
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>535</v>
+        <v>82</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
@@ -16435,19 +16421,19 @@
         <v>82</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>274</v>
+        <v>83</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>536</v>
+        <v>692</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>537</v>
+        <v>693</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>538</v>
+        <v>597</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>539</v>
+        <v>598</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>82</v>
@@ -16472,13 +16458,13 @@
         <v>82</v>
       </c>
       <c r="X116" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="Y116" t="s" s="2">
-        <v>695</v>
+        <v>82</v>
       </c>
       <c r="Z116" t="s" s="2">
-        <v>540</v>
+        <v>82</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>82</v>
@@ -16496,7 +16482,7 @@
         <v>82</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -16514,145 +16500,23 @@
         <v>82</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>541</v>
+        <v>82</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>542</v>
+        <v>600</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>543</v>
+        <v>601</v>
       </c>
       <c r="AO116" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP116" t="s" s="2">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="117" hidden="true">
-      <c r="A117" t="s" s="2">
-        <v>696</v>
-      </c>
-      <c r="B117" t="s" s="2">
-        <v>696</v>
-      </c>
-      <c r="C117" s="2"/>
-      <c r="D117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E117" s="2"/>
-      <c r="F117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G117" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K117" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="L117" t="s" s="2">
-        <v>697</v>
-      </c>
-      <c r="M117" t="s" s="2">
-        <v>698</v>
-      </c>
-      <c r="N117" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="O117" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="P117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q117" s="2"/>
-      <c r="R117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF117" t="s" s="2">
-        <v>696</v>
-      </c>
-      <c r="AG117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH117" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ117" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM117" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="AN117" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="AO117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP117" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP117">
+  <autoFilter ref="A1:AP116">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -16662,7 +16526,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI116">
+  <conditionalFormatting sqref="A2:AI115">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
